--- a/document/タスク登録機能_詳細設計書.xlsx
+++ b/document/タスク登録機能_詳細設計書.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BE8494-B20B-4570-A175-6E0D10A17E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15D07ED-86A7-4602-A78F-726E8E02399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
-    <sheet name="ユースケース記述" sheetId="7" r:id="rId2"/>
+    <sheet name="ユースケース記述 " sheetId="12" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="8" r:id="rId4"/>
     <sheet name="登録画面" sheetId="9" r:id="rId5"/>
@@ -237,16 +237,6 @@
     </rPh>
     <rPh sb="14" eb="16">
       <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ログインが成功している状態であること。</t>
-    <rPh sb="5" eb="7">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ジョウタイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -494,16 +484,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスクの期限をカレンダーから入力できるフォーム</t>
-    <rPh sb="4" eb="6">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>limitDate</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -711,251 +691,79 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">1.従業員はメニュー画面よりタスク登録ボタンを押下し、タスク登録画面に遷移する。
-2.システムはタスク登録画面を表示する。
-3.従業員は①タスク名　②カテゴリ情報　③期限　④担当者情報　⑤ステータス情報　⑥メモ　これらの登録項目を入力する。
-4:従業員は「登録」ボタンを押下する。
-5.システムは登録内容をチェックする
-6.システムは入力されたタスク情報をデーターベースに登録する。
-7.システムはタスク登録完了画面に遷移する。
-8.システムは登録完了画面を表示する。
-9.従業員は「メニュー画面へ」ボタンを押下する。
-10.システムはメニュー画面に遷移する
-</t>
-    <rPh sb="2" eb="5">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="64" eb="67">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="123" eb="126">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="148" eb="150">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="150" eb="152">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="175" eb="177">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="186" eb="188">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="222" eb="224">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="224" eb="226">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="226" eb="228">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="229" eb="231">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="237" eb="240">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="246" eb="248">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="254" eb="256">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="272" eb="274">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="275" eb="277">
-      <t>センイ</t>
+    <t>基本フロー</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1：データベース接続または登録処理に失敗した場合
+E1-1. 基本フロー6で、システムはデータベースへの登録に失敗する。
+E1-2. システムはタスク情報を登録せず、タスク登録画面を再表示する。
+E1-3. システムは「現在タスクの登録ができません。しばらくしてから再度お試しください。」というエラーメッセージを表示する。
+E1-4. 従業員は時間を置いてから再度登録を試行する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1：必須項目に未入力がある場合
+A1-1. 基本フロー5で、システムは必須項目の未入力を検出する。
+A1-2. システムはエラーメッセージを表示したタスク登録画面を再表示する。
+A1-3. 従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。
+A2：期限に過去日付が入力された場合
+A2-1. 基本フロー5で、システムは期限に過去日付が入力されていることを検出する。
+A2-2. システムは「期限に過去日付は指定できません。」というエラーメッセージを表示したタスク登録画面を再表示し、登録処理を行わない。
+A2-3. 従業員は期限を当日以降の日付に修正し、基本フロー3から再試行する。</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1. 従業員はメニュー画面より「タスク登録」ボタンを押下し、タスク登録画面へ遷移する。
+2. システムはタスク登録画面を表示する。
+3. 従業員は登録項目を入力する。
+  ・必須項目：タスク名、カテゴリ情報、担当者情報、ステータス情報
+  ・任意項目：期限、メモ　※期限を入力する場合は、本日以降の日付を指定する。
+4. 従業員は「登録」ボタンを押下する。
+5. システムは下記の入力内容をチェックする。
+   ・必須項目が入力されていること
+   ・期限が過去日付ではないこと
+6. システムは入力されたタスク情報をデータベースに登録する。
+7. システムは登録完了画面を表示する。
+8. 従業員は「メニュー画面へ」ボタンを押下する。
+9. システムはメニュー画面を表示する。</t>
+    <rPh sb="187" eb="189">
+      <t>カキ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>基本フロー</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>A1:登録項目に未入力がある場合
-A1-1:システムは基本フロー4で未入力を検出する。
-A1-2:システムはタスク登録画面を再表示する。
-A1-3:システムはエラーメッセージを表示する
-A1-3:従業員はエラーメッセージに従い入力内容を修正して基本フロー3を再試行する
-A2:データーベースへのタスク登録に失敗した場合
-A2-1:基本フロー4でシステムはタスク情報の登録に失敗する。
-A2-2:エラー画面に遷移する
-A3:期限入力フォームに過去日付が入力された場合。
-A3-1:システムは基本フロー4で過去日付の入力を検出する。
-A3-2:システムはタスク登録機能を再表示する。
-A3-3:システムはエラーメッセージ（「過去日付は登録できません」）を表示する。
-A3-4:従業員はエラーメッセージに従い未来日付を入力して基本フロー3を再試行する。</t>
-    <rPh sb="8" eb="11">
-      <t>ミニュウリョク</t>
+    <t>従業員がログインに成功している状態であること。</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウギョウ</t>
     </rPh>
-    <rPh sb="35" eb="38">
-      <t>ミニュウリョク</t>
+    <rPh sb="2" eb="3">
+      <t>イン</t>
     </rPh>
-    <rPh sb="58" eb="62">
-      <t>トウロクガメン</t>
+    <rPh sb="9" eb="11">
+      <t>セイコウ</t>
     </rPh>
-    <rPh sb="63" eb="66">
-      <t>サイヒョウジ</t>
-    </rPh>
-    <rPh sb="89" eb="91">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="112" eb="113">
-      <t>シタガ</t>
-    </rPh>
-    <rPh sb="114" eb="118">
-      <t>ニュウリョクナイヨウ</t>
-    </rPh>
-    <rPh sb="119" eb="121">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="123" eb="125">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="130" eb="133">
-      <t>サイシコウ</t>
-    </rPh>
-    <rPh sb="215" eb="217">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="217" eb="219">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="224" eb="226">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="226" eb="228">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="229" eb="231">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="234" eb="236">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="249" eb="251">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="256" eb="258">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="258" eb="260">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="261" eb="263">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="264" eb="266">
-      <t>ケンシュツ</t>
-    </rPh>
-    <rPh sb="283" eb="285">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="285" eb="287">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="288" eb="291">
-      <t>サイヒョウジ</t>
-    </rPh>
-    <rPh sb="315" eb="317">
-      <t>カコ</t>
-    </rPh>
-    <rPh sb="317" eb="319">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="320" eb="322">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="330" eb="332">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="341" eb="344">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="354" eb="355">
-      <t>シタガ</t>
-    </rPh>
-    <rPh sb="356" eb="358">
-      <t>ミライ</t>
-    </rPh>
-    <rPh sb="358" eb="360">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="361" eb="363">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="365" eb="367">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="372" eb="375">
-      <t>サイシコウ</t>
+    <rPh sb="15" eb="17">
+      <t>ジョウタイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>E1:タスク登録作業中にデータベース接続に失敗した場合
-E1-1.システムは基本フロー6でシステムはデータベース接続に失敗する。
-E1-2.システムはタスク登録画面を再表示する。
-E1-3.システムは「現在タスクの登録ができません。しばらくしてから再度お試しください。」というエラーメッセージを表示する。
-E1-4.従業員は時間を置いてから基本フロー1から再試行する。</t>
-    <rPh sb="6" eb="8">
-      <t>トウロク</t>
+    <t>タスクの期限をカレンダーから入力できるフォーム。過去日付は選択不可。</t>
+    <rPh sb="4" eb="6">
+      <t>キゲン</t>
     </rPh>
-    <rPh sb="8" eb="10">
-      <t>サギョウ</t>
+    <rPh sb="14" eb="16">
+      <t>ニュウリョク</t>
     </rPh>
-    <rPh sb="10" eb="11">
-      <t>チュウ</t>
+    <rPh sb="24" eb="26">
+      <t>カコ</t>
     </rPh>
-    <rPh sb="79" eb="81">
-      <t>トウロク</t>
+    <rPh sb="26" eb="28">
+      <t>ヒヅケ</t>
     </rPh>
-    <rPh sb="81" eb="83">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="108" eb="110">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="171" eb="173">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="179" eb="182">
-      <t>サイシコウ</t>
+    <rPh sb="29" eb="33">
+      <t>センタクフカ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1732,7 +1540,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1883,6 +1691,33 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1898,6 +1733,57 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1928,87 +1814,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2096,110 +1901,122 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4410,85 +4227,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="96"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="95"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="96"/>
-      <c r="O4" s="96"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="95"/>
+      <c r="L4" s="95"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="95"/>
+      <c r="O4" s="95"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="96"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="96"/>
-      <c r="M5" s="96"/>
-      <c r="N5" s="96"/>
-      <c r="O5" s="96"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="95"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="96"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="96"/>
-      <c r="I6" s="96"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="96"/>
-      <c r="N6" s="96"/>
-      <c r="O6" s="96"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="95"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -4508,46 +4325,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="99" t="s">
+      <c r="E8" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="95"/>
+      <c r="K8" s="95"/>
+      <c r="L8" s="95"/>
+      <c r="M8" s="95"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="92" t="s">
+      <c r="G13" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="94"/>
-      <c r="I13" s="92" t="s">
+      <c r="H13" s="93"/>
+      <c r="I13" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="93"/>
-      <c r="K13" s="94"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="93"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="92"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="93"/>
-      <c r="K14" s="94"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="93"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="92"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="93"/>
-      <c r="K15" s="94"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="93"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -4556,13 +4373,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="95" t="s">
+      <c r="G17" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="96"/>
-      <c r="I17" s="96"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="96"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="95"/>
+      <c r="K17" s="95"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -5566,7 +5383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43CE9B7-434E-4C56-93C6-9276BA3E4969}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BCA2031-1A7F-4329-99E4-E2FA41DD334F}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -5577,19 +5394,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="91" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="91" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="81"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="33" t="s">
         <v>8</v>
       </c>
@@ -5601,192 +5418,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="66" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="72">
-        <v>46177</v>
-      </c>
-      <c r="I2" s="75" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
+        <v>46189</v>
+      </c>
+      <c r="I2" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="82" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="83"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="54"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="63"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="54"/>
-    </row>
-    <row r="9" spans="1:10" ht="145.5" customHeight="1">
-      <c r="A9" s="60" t="s">
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="63"/>
+    </row>
+    <row r="9" spans="1:10" ht="203.25" customHeight="1">
+      <c r="A9" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="61"/>
+      <c r="D9" s="90" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="64" t="s">
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="63"/>
+    </row>
+    <row r="10" spans="1:10" ht="154.5" customHeight="1">
+      <c r="A10" s="87"/>
+      <c r="B10" s="89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="61"/>
+      <c r="D10" s="158" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="54"/>
-    </row>
-    <row r="10" spans="1:10" ht="295.5" customHeight="1">
-      <c r="A10" s="61"/>
-      <c r="B10" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="54"/>
-    </row>
-    <row r="11" spans="1:10" ht="144.75" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="63" t="s">
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+      <c r="G10" s="156"/>
+      <c r="H10" s="156"/>
+      <c r="I10" s="156"/>
+      <c r="J10" s="157"/>
+    </row>
+    <row r="11" spans="1:10" ht="84" customHeight="1">
+      <c r="A11" s="88"/>
+      <c r="B11" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="65" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="54"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="155" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="156"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="156"/>
+      <c r="H11" s="156"/>
+      <c r="I11" s="156"/>
+      <c r="J11" s="157"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="53" t="s">
+      <c r="B12" s="60"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="54"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="63"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="59"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="85"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6777,6 +6594,17 @@
     <row r="1000" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A7:C7"/>
@@ -6793,17 +6621,6 @@
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6822,19 +6639,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="114" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="114" t="s">
+      <c r="E1" s="114"/>
+      <c r="F1" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="115"/>
+      <c r="G1" s="114"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -6846,40 +6663,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="109"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="103"/>
+      <c r="A2" s="108"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="102"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="109"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="104"/>
+      <c r="A3" s="108"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="111"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="113"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="105"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -8236,19 +8053,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="91" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="91" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="81"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -8260,48 +8077,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="66" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="72">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46181</v>
       </c>
-      <c r="I2" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="76"/>
+      <c r="I2" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="41"/>
@@ -9649,25 +9466,26 @@
     <col min="1" max="3" width="5.140625" style="31" customWidth="1"/>
     <col min="4" max="6" width="16.7109375" style="31" customWidth="1"/>
     <col min="7" max="7" width="22" style="31" customWidth="1"/>
-    <col min="8" max="10" width="16.7109375" style="31" customWidth="1"/>
+    <col min="8" max="9" width="16.7109375" style="31" customWidth="1"/>
+    <col min="10" max="10" width="40.28515625" style="31" customWidth="1"/>
     <col min="11" max="26" width="8.7109375" style="31" customWidth="1"/>
     <col min="27" max="16384" width="14.42578125" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="91" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="91" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="81"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -9679,203 +9497,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="66" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="72">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46178</v>
       </c>
-      <c r="I2" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="76"/>
+      <c r="I2" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="87"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="123" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="83"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="127" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="126"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
+      <c r="A7" s="122"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="124"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="87"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="129"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="125"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="87"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="88"/>
-      <c r="I9" s="88"/>
-      <c r="J9" s="129"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="125"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="87"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="129"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="125"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="129"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="125"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="87"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="88"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="88"/>
-      <c r="I12" s="88"/>
-      <c r="J12" s="129"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="125"/>
     </row>
     <row r="13" spans="1:10" ht="165.75" customHeight="1">
-      <c r="A13" s="87"/>
-      <c r="B13" s="88"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="129"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="125"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="124" t="s">
+      <c r="A14" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="54"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="63"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="52"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="46" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="47" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="46" t="s">
         <v>29</v>
       </c>
@@ -9888,248 +9706,248 @@
       <c r="G16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="54"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="63"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="121" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="52"/>
+      <c r="A17" s="128" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="60"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="44" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F17" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="60"/>
+      <c r="J17" s="63"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="128" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="60"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" s="62" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" s="60"/>
+      <c r="J18" s="63"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="128" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="60"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="60"/>
+      <c r="J19" s="63"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="128" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="60"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="I20" s="60"/>
+      <c r="J20" s="63"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="128" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" s="60"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="I21" s="60"/>
+      <c r="J21" s="63"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="128" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="60"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="60"/>
+      <c r="J22" s="63"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="128" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="60"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23" s="60"/>
+      <c r="J23" s="63"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="128" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="60"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="G17" s="43" t="s">
+      <c r="F24" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="I24" s="60"/>
+      <c r="J24" s="63"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="128" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="60"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="53" t="s">
-        <v>115</v>
-      </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="54"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="121" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="43" t="s">
+      <c r="F25" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="I25" s="60"/>
+      <c r="J25" s="63"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A26" s="128" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="60"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="45" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="H18" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="I18" s="51"/>
-      <c r="J18" s="54"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="121" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="F19" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="H19" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="51"/>
-      <c r="J19" s="54"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="121" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="I20" s="51"/>
-      <c r="J20" s="54"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="121" t="s">
-        <v>100</v>
-      </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="F21" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="G21" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" s="53" t="s">
-        <v>96</v>
-      </c>
-      <c r="I21" s="51"/>
-      <c r="J21" s="54"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="121" t="s">
-        <v>95</v>
-      </c>
-      <c r="B22" s="51"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="I22" s="51"/>
-      <c r="J22" s="54"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="121" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="H23" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="I23" s="51"/>
-      <c r="J23" s="54"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="121" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="51"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="G24" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="H24" s="53" t="s">
-        <v>82</v>
-      </c>
-      <c r="I24" s="51"/>
-      <c r="J24" s="54"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="121" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="I25" s="51"/>
-      <c r="J25" s="54"/>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A26" s="121" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="44" t="s">
-        <v>76</v>
-      </c>
       <c r="F26" s="43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="I26" s="56"/>
-      <c r="J26" s="59"/>
+      <c r="H26" s="84" t="s">
+        <v>73</v>
+      </c>
+      <c r="I26" s="82"/>
+      <c r="J26" s="85"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11110,11 +10928,26 @@
     <row r="1003" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
@@ -11127,26 +10960,11 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11171,19 +10989,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="91" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="91" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="81"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -11195,204 +11013,204 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="66" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="72">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46178</v>
       </c>
-      <c r="I2" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="76"/>
+      <c r="I2" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="87"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:16" ht="28.5" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="123" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="83"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="127" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:16" ht="21" customHeight="1">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:16" ht="21" customHeight="1">
-      <c r="A7" s="126"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
+      <c r="A7" s="122"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="124"/>
     </row>
     <row r="8" spans="1:16" ht="21" customHeight="1">
-      <c r="A8" s="87"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="129"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="125"/>
     </row>
     <row r="9" spans="1:16" ht="21" customHeight="1">
-      <c r="A9" s="87"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="88"/>
-      <c r="I9" s="88"/>
-      <c r="J9" s="129"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="125"/>
     </row>
     <row r="10" spans="1:16" ht="21" customHeight="1">
-      <c r="A10" s="87"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="129"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="125"/>
     </row>
     <row r="11" spans="1:16" ht="21" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="129"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="125"/>
     </row>
     <row r="12" spans="1:16" ht="21" customHeight="1">
-      <c r="A12" s="87"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="88"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="88"/>
-      <c r="I12" s="88"/>
-      <c r="J12" s="129"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="125"/>
     </row>
     <row r="13" spans="1:16" ht="129.75" customHeight="1">
-      <c r="A13" s="87"/>
-      <c r="B13" s="88"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="129"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="125"/>
       <c r="P13" s="48"/>
     </row>
     <row r="14" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A14" s="124" t="s">
+      <c r="A14" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="54"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="63"/>
     </row>
     <row r="15" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="52"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="46" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="47" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="46" t="s">
         <v>29</v>
       </c>
@@ -11405,83 +11223,83 @@
       <c r="G16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="54"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="63"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="131" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="52"/>
+      <c r="A17" s="129" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="60"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="44" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="54"/>
+        <v>74</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="60"/>
+      <c r="J17" s="63"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="131" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
+      <c r="A18" s="129" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="60"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" s="51"/>
-      <c r="J18" s="54"/>
+        <v>74</v>
+      </c>
+      <c r="H18" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="60"/>
+      <c r="J18" s="63"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="131"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
+      <c r="A19" s="129"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="44"/>
       <c r="E19" s="44"/>
       <c r="F19" s="44"/>
       <c r="G19" s="44"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="54"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="63"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A20" s="130"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="57"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="83"/>
       <c r="D20" s="45"/>
       <c r="E20" s="45"/>
       <c r="F20" s="45"/>
       <c r="G20" s="45"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="59"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="85"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12462,6 +12280,15 @@
     <row r="997" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
@@ -12478,15 +12305,6 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12510,19 +12328,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="91" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="81"/>
-      <c r="F1" s="91" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="81"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -12534,203 +12352,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="66" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="72">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46178</v>
       </c>
-      <c r="I2" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="76"/>
+      <c r="I2" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="87"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="77"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="87"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="77"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="122" t="s">
+      <c r="A5" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="123" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="83"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="126"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
+      <c r="A7" s="122"/>
+      <c r="B7" s="123"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="123"/>
+      <c r="H7" s="123"/>
+      <c r="I7" s="123"/>
+      <c r="J7" s="124"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="87"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
-      <c r="J8" s="129"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="125"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="87"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="88"/>
-      <c r="I9" s="88"/>
-      <c r="J9" s="129"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="125"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="87"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="129"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="125"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="129"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="125"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="87"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="88"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="88"/>
-      <c r="I12" s="88"/>
-      <c r="J12" s="129"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="125"/>
     </row>
     <row r="13" spans="1:10" ht="141" customHeight="1">
-      <c r="A13" s="87"/>
-      <c r="B13" s="88"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
-      <c r="I13" s="88"/>
-      <c r="J13" s="129"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="125"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="124" t="s">
+      <c r="A14" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="54"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="63"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="124" t="s">
+      <c r="A15" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="52"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="46" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="47" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="46" t="s">
         <v>29</v>
       </c>
@@ -12743,71 +12561,71 @@
       <c r="G16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="125" t="s">
+      <c r="H16" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="54"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="63"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="131" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="52"/>
+      <c r="A17" s="129" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="60"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="44" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="53" t="s">
-        <v>124</v>
-      </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="54"/>
+        <v>74</v>
+      </c>
+      <c r="H17" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="60"/>
+      <c r="J17" s="63"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="131" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
+      <c r="A18" s="129" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="60"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" s="51"/>
-      <c r="J18" s="54"/>
+        <v>74</v>
+      </c>
+      <c r="H18" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="60"/>
+      <c r="J18" s="63"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A19" s="130"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="57"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="83"/>
       <c r="D19" s="45"/>
       <c r="E19" s="45"/>
       <c r="F19" s="49"/>
       <c r="G19" s="49"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="59"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="85"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13788,16 +13606,6 @@
     <row r="996" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
@@ -13811,6 +13619,16 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13830,182 +13648,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="153" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="114" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="114" t="s">
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="114" t="s">
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="114" t="s">
+      <c r="P1" s="114"/>
+      <c r="Q1" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="115"/>
-      <c r="S1" s="114" t="s">
+      <c r="R1" s="114"/>
+      <c r="S1" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="145"/>
+      <c r="T1" s="142"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="109"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="139"/>
-      <c r="M2" s="139"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="117"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="117"/>
-      <c r="S2" s="116"/>
-      <c r="T2" s="140"/>
+      <c r="A2" s="108"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="115"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="115"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="115"/>
+      <c r="T2" s="150"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="109"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="118"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="118"/>
-      <c r="P3" s="110"/>
-      <c r="Q3" s="118"/>
-      <c r="R3" s="110"/>
-      <c r="S3" s="118"/>
-      <c r="T3" s="141"/>
+      <c r="A3" s="108"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="109"/>
+      <c r="O3" s="117"/>
+      <c r="P3" s="109"/>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="109"/>
+      <c r="S3" s="117"/>
+      <c r="T3" s="151"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="111"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="119"/>
-      <c r="R4" s="113"/>
-      <c r="S4" s="119"/>
-      <c r="T4" s="142"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="112"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="112"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="152"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="146" t="s">
+      <c r="A5" s="139" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="144"/>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="144"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="147" t="s">
+      <c r="B5" s="140"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="141" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="144"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="144"/>
-      <c r="K5" s="144"/>
-      <c r="L5" s="144"/>
-      <c r="M5" s="144"/>
-      <c r="N5" s="144"/>
-      <c r="O5" s="144"/>
-      <c r="P5" s="144"/>
-      <c r="Q5" s="144"/>
-      <c r="R5" s="144"/>
-      <c r="S5" s="144"/>
-      <c r="T5" s="145"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="140"/>
+      <c r="S5" s="140"/>
+      <c r="T5" s="142"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="148" t="s">
+      <c r="A6" s="143" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="149" t="s">
+      <c r="B6" s="92"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="93"/>
-      <c r="P6" s="93"/>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="93"/>
-      <c r="S6" s="93"/>
-      <c r="T6" s="150"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="92"/>
+      <c r="Q6" s="92"/>
+      <c r="R6" s="92"/>
+      <c r="S6" s="92"/>
+      <c r="T6" s="145"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="148" t="s">
+      <c r="A7" s="143" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="93"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="93"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="149" t="s">
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="144" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="93"/>
-      <c r="P7" s="93"/>
-      <c r="Q7" s="93"/>
-      <c r="R7" s="93"/>
-      <c r="S7" s="93"/>
-      <c r="T7" s="150"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="92"/>
+      <c r="Q7" s="92"/>
+      <c r="R7" s="92"/>
+      <c r="S7" s="92"/>
+      <c r="T7" s="145"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -14204,37 +14022,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="148" t="s">
+      <c r="A15" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="94"/>
-      <c r="C15" s="153" t="s">
+      <c r="B15" s="93"/>
+      <c r="C15" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="94"/>
-      <c r="E15" s="132" t="s">
+      <c r="D15" s="93"/>
+      <c r="E15" s="147" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="94"/>
-      <c r="G15" s="132" t="s">
+      <c r="F15" s="93"/>
+      <c r="G15" s="147" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="93"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="132" t="s">
+      <c r="H15" s="92"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="147" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="94"/>
-      <c r="L15" s="132" t="s">
+      <c r="K15" s="93"/>
+      <c r="L15" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="93"/>
-      <c r="N15" s="94"/>
-      <c r="O15" s="132" t="s">
+      <c r="M15" s="92"/>
+      <c r="N15" s="93"/>
+      <c r="O15" s="147" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="93"/>
-      <c r="Q15" s="94"/>
+      <c r="P15" s="92"/>
+      <c r="Q15" s="93"/>
       <c r="R15" s="13" t="s">
         <v>51</v>
       </c>
@@ -14246,37 +14064,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="151">
+      <c r="A16" s="131">
         <v>1</v>
       </c>
-      <c r="B16" s="94"/>
-      <c r="C16" s="152" t="s">
+      <c r="B16" s="93"/>
+      <c r="C16" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="94"/>
-      <c r="E16" s="152" t="s">
+      <c r="D16" s="93"/>
+      <c r="E16" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="94"/>
-      <c r="G16" s="133" t="s">
+      <c r="F16" s="93"/>
+      <c r="G16" s="146" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="93"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="133" t="s">
+      <c r="H16" s="92"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="146" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="94"/>
-      <c r="L16" s="137" t="s">
+      <c r="K16" s="93"/>
+      <c r="L16" s="136" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="93"/>
-      <c r="N16" s="94"/>
-      <c r="O16" s="137" t="s">
+      <c r="M16" s="92"/>
+      <c r="N16" s="93"/>
+      <c r="O16" s="136" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="93"/>
-      <c r="Q16" s="94"/>
+      <c r="P16" s="92"/>
+      <c r="Q16" s="93"/>
       <c r="R16" s="26"/>
       <c r="S16" s="26"/>
       <c r="T16" s="27"/>
@@ -14288,37 +14106,37 @@
       <c r="Z16" s="28"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="151">
+      <c r="A17" s="131">
         <v>2</v>
       </c>
-      <c r="B17" s="94"/>
-      <c r="C17" s="152" t="s">
+      <c r="B17" s="93"/>
+      <c r="C17" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="94"/>
-      <c r="E17" s="152" t="s">
+      <c r="D17" s="93"/>
+      <c r="E17" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="133" t="s">
+      <c r="F17" s="93"/>
+      <c r="G17" s="146" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="93"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="133" t="s">
+      <c r="H17" s="92"/>
+      <c r="I17" s="93"/>
+      <c r="J17" s="146" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="94"/>
-      <c r="L17" s="137" t="s">
+      <c r="K17" s="93"/>
+      <c r="L17" s="136" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="93"/>
-      <c r="N17" s="94"/>
-      <c r="O17" s="137" t="s">
+      <c r="M17" s="92"/>
+      <c r="N17" s="93"/>
+      <c r="O17" s="136" t="s">
         <v>65</v>
       </c>
-      <c r="P17" s="93"/>
-      <c r="Q17" s="94"/>
+      <c r="P17" s="92"/>
+      <c r="Q17" s="93"/>
       <c r="R17" s="26"/>
       <c r="S17" s="26"/>
       <c r="T17" s="27"/>
@@ -14330,23 +14148,23 @@
       <c r="Z17" s="28"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="151"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="152"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="133"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="133"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="137"/>
-      <c r="M18" s="93"/>
-      <c r="N18" s="94"/>
-      <c r="O18" s="137"/>
-      <c r="P18" s="93"/>
-      <c r="Q18" s="94"/>
+      <c r="A18" s="131"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="146"/>
+      <c r="H18" s="92"/>
+      <c r="I18" s="93"/>
+      <c r="J18" s="146"/>
+      <c r="K18" s="93"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="92"/>
+      <c r="N18" s="93"/>
+      <c r="O18" s="136"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="93"/>
       <c r="R18" s="26"/>
       <c r="S18" s="26"/>
       <c r="T18" s="27"/>
@@ -14358,23 +14176,23 @@
       <c r="Z18" s="28"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="151"/>
-      <c r="B19" s="94"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="133"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="137"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="137"/>
-      <c r="P19" s="93"/>
-      <c r="Q19" s="94"/>
+      <c r="A19" s="131"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="132"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="146"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="146"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="93"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="93"/>
       <c r="R19" s="26"/>
       <c r="S19" s="26"/>
       <c r="T19" s="27"/>
@@ -14386,23 +14204,23 @@
       <c r="Z19" s="28"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="151"/>
-      <c r="B20" s="94"/>
-      <c r="C20" s="152"/>
-      <c r="D20" s="94"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="94"/>
-      <c r="G20" s="133"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="94"/>
-      <c r="J20" s="133"/>
-      <c r="K20" s="94"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="93"/>
-      <c r="N20" s="94"/>
-      <c r="O20" s="137"/>
-      <c r="P20" s="93"/>
-      <c r="Q20" s="94"/>
+      <c r="A20" s="131"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="132"/>
+      <c r="D20" s="93"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="146"/>
+      <c r="H20" s="92"/>
+      <c r="I20" s="93"/>
+      <c r="J20" s="146"/>
+      <c r="K20" s="93"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="92"/>
+      <c r="N20" s="93"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="92"/>
+      <c r="Q20" s="93"/>
       <c r="R20" s="26"/>
       <c r="S20" s="26"/>
       <c r="T20" s="27"/>
@@ -14414,23 +14232,23 @@
       <c r="Z20" s="28"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="151"/>
-      <c r="B21" s="94"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="94"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="94"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="93"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="137"/>
-      <c r="M21" s="93"/>
-      <c r="N21" s="94"/>
-      <c r="O21" s="137"/>
-      <c r="P21" s="93"/>
-      <c r="Q21" s="94"/>
+      <c r="A21" s="131"/>
+      <c r="B21" s="93"/>
+      <c r="C21" s="132"/>
+      <c r="D21" s="93"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="93"/>
+      <c r="G21" s="146"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="93"/>
+      <c r="J21" s="146"/>
+      <c r="K21" s="93"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="93"/>
+      <c r="O21" s="136"/>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="93"/>
       <c r="R21" s="26"/>
       <c r="S21" s="26"/>
       <c r="T21" s="27"/>
@@ -14442,23 +14260,23 @@
       <c r="Z21" s="28"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="151"/>
-      <c r="B22" s="94"/>
-      <c r="C22" s="152"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="152"/>
-      <c r="F22" s="94"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="93"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="133"/>
-      <c r="K22" s="94"/>
-      <c r="L22" s="137"/>
-      <c r="M22" s="93"/>
-      <c r="N22" s="94"/>
-      <c r="O22" s="137"/>
-      <c r="P22" s="93"/>
-      <c r="Q22" s="94"/>
+      <c r="A22" s="131"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="132"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="146"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="146"/>
+      <c r="K22" s="93"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="92"/>
+      <c r="N22" s="93"/>
+      <c r="O22" s="136"/>
+      <c r="P22" s="92"/>
+      <c r="Q22" s="93"/>
       <c r="R22" s="26"/>
       <c r="S22" s="26"/>
       <c r="T22" s="27"/>
@@ -14470,23 +14288,23 @@
       <c r="Z22" s="28"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="151"/>
-      <c r="B23" s="94"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="94"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="94"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="93"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="133"/>
-      <c r="K23" s="94"/>
-      <c r="L23" s="137"/>
-      <c r="M23" s="93"/>
-      <c r="N23" s="94"/>
-      <c r="O23" s="137"/>
-      <c r="P23" s="93"/>
-      <c r="Q23" s="94"/>
+      <c r="A23" s="131"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="132"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="132"/>
+      <c r="F23" s="93"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="93"/>
+      <c r="O23" s="136"/>
+      <c r="P23" s="92"/>
+      <c r="Q23" s="93"/>
       <c r="R23" s="26"/>
       <c r="S23" s="26"/>
       <c r="T23" s="27"/>
@@ -14498,23 +14316,23 @@
       <c r="Z23" s="28"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="151"/>
-      <c r="B24" s="94"/>
-      <c r="C24" s="152"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="152"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="93"/>
-      <c r="I24" s="94"/>
-      <c r="J24" s="133"/>
-      <c r="K24" s="94"/>
-      <c r="L24" s="137"/>
-      <c r="M24" s="93"/>
-      <c r="N24" s="94"/>
-      <c r="O24" s="137"/>
-      <c r="P24" s="93"/>
-      <c r="Q24" s="94"/>
+      <c r="A24" s="131"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="132"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="146"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="146"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="136"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="93"/>
+      <c r="O24" s="136"/>
+      <c r="P24" s="92"/>
+      <c r="Q24" s="93"/>
       <c r="R24" s="26"/>
       <c r="S24" s="26"/>
       <c r="T24" s="27"/>
@@ -14526,23 +14344,23 @@
       <c r="Z24" s="28"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="151"/>
-      <c r="B25" s="94"/>
-      <c r="C25" s="152"/>
-      <c r="D25" s="94"/>
-      <c r="E25" s="152"/>
-      <c r="F25" s="94"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="93"/>
-      <c r="I25" s="94"/>
-      <c r="J25" s="133"/>
-      <c r="K25" s="94"/>
-      <c r="L25" s="137"/>
-      <c r="M25" s="93"/>
-      <c r="N25" s="94"/>
-      <c r="O25" s="137"/>
-      <c r="P25" s="93"/>
-      <c r="Q25" s="94"/>
+      <c r="A25" s="131"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="132"/>
+      <c r="D25" s="93"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="146"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="146"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="92"/>
+      <c r="N25" s="93"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="92"/>
+      <c r="Q25" s="93"/>
       <c r="R25" s="26"/>
       <c r="S25" s="26"/>
       <c r="T25" s="27"/>
@@ -14554,23 +14372,23 @@
       <c r="Z25" s="28"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="151"/>
-      <c r="B26" s="94"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="94"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="94"/>
-      <c r="G26" s="133"/>
-      <c r="H26" s="93"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="133"/>
-      <c r="K26" s="94"/>
-      <c r="L26" s="137"/>
-      <c r="M26" s="93"/>
-      <c r="N26" s="94"/>
-      <c r="O26" s="137"/>
-      <c r="P26" s="93"/>
-      <c r="Q26" s="94"/>
+      <c r="A26" s="131"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="146"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="146"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="136"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="93"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="92"/>
+      <c r="Q26" s="93"/>
       <c r="R26" s="26"/>
       <c r="S26" s="26"/>
       <c r="T26" s="27"/>
@@ -14582,23 +14400,23 @@
       <c r="Z26" s="28"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="151"/>
-      <c r="B27" s="94"/>
-      <c r="C27" s="152"/>
-      <c r="D27" s="94"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="94"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="94"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="94"/>
-      <c r="L27" s="137"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="94"/>
-      <c r="O27" s="137"/>
-      <c r="P27" s="93"/>
-      <c r="Q27" s="94"/>
+      <c r="A27" s="131"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="132"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="146"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="146"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="92"/>
+      <c r="N27" s="93"/>
+      <c r="O27" s="136"/>
+      <c r="P27" s="92"/>
+      <c r="Q27" s="93"/>
       <c r="R27" s="26"/>
       <c r="S27" s="26"/>
       <c r="T27" s="27"/>
@@ -14610,23 +14428,23 @@
       <c r="Z27" s="28"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="151"/>
-      <c r="B28" s="94"/>
-      <c r="C28" s="152"/>
-      <c r="D28" s="94"/>
-      <c r="E28" s="152"/>
-      <c r="F28" s="94"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="93"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="133"/>
-      <c r="K28" s="94"/>
-      <c r="L28" s="137"/>
-      <c r="M28" s="93"/>
-      <c r="N28" s="94"/>
-      <c r="O28" s="137"/>
-      <c r="P28" s="93"/>
-      <c r="Q28" s="94"/>
+      <c r="A28" s="131"/>
+      <c r="B28" s="93"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="93"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="93"/>
+      <c r="G28" s="146"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="146"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="136"/>
+      <c r="M28" s="92"/>
+      <c r="N28" s="93"/>
+      <c r="O28" s="136"/>
+      <c r="P28" s="92"/>
+      <c r="Q28" s="93"/>
       <c r="R28" s="26"/>
       <c r="S28" s="26"/>
       <c r="T28" s="27"/>
@@ -14638,23 +14456,23 @@
       <c r="Z28" s="28"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="151"/>
-      <c r="B29" s="94"/>
-      <c r="C29" s="152"/>
-      <c r="D29" s="94"/>
-      <c r="E29" s="152"/>
-      <c r="F29" s="94"/>
-      <c r="G29" s="133"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="94"/>
-      <c r="J29" s="133"/>
-      <c r="K29" s="94"/>
-      <c r="L29" s="137"/>
-      <c r="M29" s="93"/>
-      <c r="N29" s="94"/>
-      <c r="O29" s="137"/>
-      <c r="P29" s="93"/>
-      <c r="Q29" s="94"/>
+      <c r="A29" s="131"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="132"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="146"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="146"/>
+      <c r="K29" s="93"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="92"/>
+      <c r="N29" s="93"/>
+      <c r="O29" s="136"/>
+      <c r="P29" s="92"/>
+      <c r="Q29" s="93"/>
       <c r="R29" s="26"/>
       <c r="S29" s="26"/>
       <c r="T29" s="27"/>
@@ -14666,23 +14484,23 @@
       <c r="Z29" s="28"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="151"/>
-      <c r="B30" s="94"/>
-      <c r="C30" s="152"/>
-      <c r="D30" s="94"/>
-      <c r="E30" s="152"/>
-      <c r="F30" s="94"/>
-      <c r="G30" s="133"/>
-      <c r="H30" s="93"/>
-      <c r="I30" s="94"/>
-      <c r="J30" s="133"/>
-      <c r="K30" s="94"/>
-      <c r="L30" s="137"/>
-      <c r="M30" s="93"/>
-      <c r="N30" s="94"/>
-      <c r="O30" s="137"/>
-      <c r="P30" s="93"/>
-      <c r="Q30" s="94"/>
+      <c r="A30" s="131"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="132"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="146"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="93"/>
+      <c r="J30" s="146"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="136"/>
+      <c r="M30" s="92"/>
+      <c r="N30" s="93"/>
+      <c r="O30" s="136"/>
+      <c r="P30" s="92"/>
+      <c r="Q30" s="93"/>
       <c r="R30" s="26"/>
       <c r="S30" s="26"/>
       <c r="T30" s="27"/>
@@ -14694,23 +14512,23 @@
       <c r="Z30" s="28"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="154"/>
-      <c r="B31" s="136"/>
-      <c r="C31" s="155"/>
-      <c r="D31" s="136"/>
-      <c r="E31" s="155"/>
-      <c r="F31" s="136"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="135"/>
-      <c r="I31" s="136"/>
-      <c r="J31" s="134"/>
-      <c r="K31" s="136"/>
-      <c r="L31" s="138"/>
-      <c r="M31" s="135"/>
-      <c r="N31" s="136"/>
-      <c r="O31" s="138"/>
-      <c r="P31" s="135"/>
-      <c r="Q31" s="136"/>
+      <c r="A31" s="133"/>
+      <c r="B31" s="134"/>
+      <c r="C31" s="135"/>
+      <c r="D31" s="134"/>
+      <c r="E31" s="135"/>
+      <c r="F31" s="134"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="134"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="134"/>
+      <c r="L31" s="137"/>
+      <c r="M31" s="138"/>
+      <c r="N31" s="134"/>
+      <c r="O31" s="137"/>
+      <c r="P31" s="138"/>
+      <c r="Q31" s="134"/>
       <c r="R31" s="29"/>
       <c r="S31" s="29"/>
       <c r="T31" s="30"/>
@@ -15708,6 +15526,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -15732,118 +15662,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク登録機能_詳細設計書.xlsx
+++ b/document/タスク登録機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A4795C-3BE4-4E09-A161-E2CF4267A5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7CF31E-9062-49BC-8D41-01DAFE0400EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -691,17 +691,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>A1：必須項目に未入力がある場合
-A1-1. 基本フロー5で、システムは必須項目の未入力を検出する。
-A1-2. システムはエラーメッセージを表示したタスク登録画面を再表示する。
-A1-3. 従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。
-A2：期限に過去日付が入力された場合
-A2-1. 基本フロー5で、システムは期限に過去日付が入力されていることを検出する。
-A2-2. システムは「期限に過去日付は指定できません。」というエラーメッセージを表示したタスク登録画面を再表示し、登録処理を行わない。
-A2-3. 従業員は期限を当日以降の日付に修正し、基本フロー3から再試行する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>1. 従業員はメニュー画面より「タスク登録」ボタンを押下し、タスク登録画面へ遷移する。
 2. システムはタスク登録画面を表示する。
 3. 従業員は登録項目を入力する。
@@ -800,6 +789,109 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1：必須項目に未入力がある場合
+A1-1. 基本フロー5で、システムは必須項目の未入力を検出する。
+A1-2. システムはエラーメッセージを表示したタスク登録画面を再表示する。
+A1-3. 従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。
+A2：期限に過去日付が入力された場合
+A2-1. 基本フロー5で、システムは期限に過去日付が入力されていることを検出する。
+A2-2. システムは「期限に過去日付は指定できません。」というエラーメッセージを表示したタスク登録画面を再表示し、登録処理を行わない。
+A2-3. 従業員は期限を当日以降の日付に修正し、基本フロー3から再試行する。
+A3:タスク名の文字数が50文字を超過する場合
+A3-1:基本フロー5で、システムはタスク名の文字数に50文字を超える入力されていることを検出する。
+A3-2:システムは「タスク名は50文字以内で入力してください。」というエラーメッセージを表示したタスク登録画面を再表示する。
+A3-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。
+A4:メモの文字数が100文字を超過する場合
+A4-1:基本フロー5で、システムはメモの文字数に100文字を超える入力されていることを検出する。
+A4-2:システムは「メモは100文字以内で入力してください。」というエラーメッセージを表示したタスク登録画面を再表示する。
+A4-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。</t>
+    <rPh sb="314" eb="315">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="316" eb="319">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="322" eb="324">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="325" eb="327">
+      <t>チョウカ</t>
+    </rPh>
+    <rPh sb="329" eb="331">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="353" eb="354">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="355" eb="358">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="361" eb="363">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="364" eb="365">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="397" eb="398">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="401" eb="403">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="403" eb="405">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="406" eb="408">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="428" eb="430">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="435" eb="437">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="437" eb="439">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="440" eb="443">
+      <t>サイヒョウジ</t>
+    </rPh>
+    <rPh sb="452" eb="455">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="465" eb="466">
+      <t>シタガ</t>
+    </rPh>
+    <rPh sb="467" eb="469">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="469" eb="471">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="472" eb="474">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="476" eb="478">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="484" eb="487">
+      <t>サイシコウ</t>
+    </rPh>
+    <rPh sb="498" eb="501">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="505" eb="507">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="508" eb="510">
+      <t>チョウカ</t>
+    </rPh>
+    <rPh sb="512" eb="514">
+      <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1727,63 +1819,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1809,6 +1844,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1861,6 +1911,48 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1952,12 +2044,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1976,32 +2062,71 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2018,41 +2143,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5569,19 +5661,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="94" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="84"/>
-      <c r="F1" s="94" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="84"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="33" t="s">
         <v>8</v>
       </c>
@@ -5593,192 +5685,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="69" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="69" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="75">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46189</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="79"/>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="90"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="80"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="92"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="81"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="85" t="s">
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="86"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="53" t="s">
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="54"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53" t="s">
+      <c r="B7" s="60"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="54"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="63"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53" t="s">
-        <v>128</v>
-      </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="54"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="63"/>
     </row>
     <row r="9" spans="1:10" ht="203.25" customHeight="1">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="64" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="54"/>
-    </row>
-    <row r="10" spans="1:10" ht="154.5" customHeight="1">
-      <c r="A10" s="61"/>
-      <c r="B10" s="63" t="s">
+      <c r="C9" s="61"/>
+      <c r="D9" s="90" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="63"/>
+    </row>
+    <row r="10" spans="1:10" ht="289.5" customHeight="1">
+      <c r="A10" s="87"/>
+      <c r="B10" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="67"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="91" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="93"/>
     </row>
     <row r="11" spans="1:10" ht="84" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="63" t="s">
+      <c r="A11" s="88"/>
+      <c r="B11" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="68" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="94" t="s">
         <v>125</v>
       </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="67"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="93"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="53" t="s">
+      <c r="B12" s="60"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="54"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="63"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="59"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="85"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6769,6 +6861,17 @@
     <row r="1000" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A7:C7"/>
@@ -6785,17 +6888,6 @@
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -8231,16 +8323,16 @@
       <c r="A1" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="94" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="84"/>
-      <c r="F1" s="94" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="84"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -8252,48 +8344,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="69" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="69" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="75">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46181</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="79"/>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="90"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="80"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="92"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="81"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="41"/>
@@ -9651,16 +9743,16 @@
       <c r="A1" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="94" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="84"/>
-      <c r="F1" s="94" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="84"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -9672,190 +9764,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="69" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="69" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="75">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46178</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="79"/>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="90"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="80"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="126" t="s">
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="132" t="s">
         <v>116</v>
       </c>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="86"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="129"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="131"/>
+      <c r="A7" s="127"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="129"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="90"/>
-      <c r="B8" s="91"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="132"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="130"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="90"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="132"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="130"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="90"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="132"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="130"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="132"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="130"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="90"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="132"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="130"/>
     </row>
     <row r="13" spans="1:10" ht="165.75" customHeight="1">
-      <c r="A13" s="90"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="132"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="130"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="125" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="54"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="63"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53" t="s">
+      <c r="B15" s="60"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="52"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="46" t="s">
         <v>27</v>
       </c>
@@ -9864,11 +9956,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="127" t="s">
+      <c r="A16" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="46" t="s">
         <v>29</v>
       </c>
@@ -9881,18 +9973,18 @@
       <c r="G16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="128" t="s">
+      <c r="H16" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="54"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="63"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="124" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="52"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="44" t="s">
         <v>112</v>
       </c>
@@ -9905,18 +9997,18 @@
       <c r="G17" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="54"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="63"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="124" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="44" t="s">
         <v>108</v>
       </c>
@@ -9929,18 +10021,18 @@
       <c r="G18" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="H18" s="53" t="s">
+      <c r="H18" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="I18" s="51"/>
-      <c r="J18" s="54"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="63"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="124" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="44" t="s">
         <v>104</v>
       </c>
@@ -9951,20 +10043,20 @@
         <v>103</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="H19" s="53" t="s">
+        <v>130</v>
+      </c>
+      <c r="H19" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="I19" s="51"/>
-      <c r="J19" s="54"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="63"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="124" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="52"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="44" t="s">
         <v>100</v>
       </c>
@@ -9977,18 +10069,18 @@
       <c r="G20" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="H20" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="I20" s="51"/>
-      <c r="J20" s="54"/>
+      <c r="H20" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="60"/>
+      <c r="J20" s="63"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="124" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="52"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="61"/>
       <c r="D21" s="44" t="s">
         <v>96</v>
       </c>
@@ -9999,20 +10091,20 @@
         <v>95</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="H21" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="H21" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="I21" s="51"/>
-      <c r="J21" s="54"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="63"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="124" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="51"/>
-      <c r="C22" s="52"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="61"/>
       <c r="D22" s="44" t="s">
         <v>92</v>
       </c>
@@ -10020,23 +10112,23 @@
         <v>91</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G22" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="H22" s="53" t="s">
+      <c r="H22" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="I22" s="51"/>
-      <c r="J22" s="54"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="63"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="124" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="52"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="61"/>
       <c r="D23" s="44" t="s">
         <v>87</v>
       </c>
@@ -10049,18 +10141,18 @@
       <c r="G23" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="H23" s="53" t="s">
+      <c r="H23" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="I23" s="51"/>
-      <c r="J23" s="54"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="63"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
       <c r="A24" s="124" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="51"/>
-      <c r="C24" s="52"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="61"/>
       <c r="D24" s="44" t="s">
         <v>82</v>
       </c>
@@ -10071,41 +10163,41 @@
         <v>74</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="H24" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="H24" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="I24" s="51"/>
-      <c r="J24" s="54"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="63"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
       <c r="A25" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="52"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="61"/>
       <c r="D25" s="44" t="s">
         <v>79</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F25" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="H25" s="53" t="s">
+      <c r="H25" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="I25" s="51"/>
-      <c r="J25" s="54"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="63"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A26" s="124" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="52"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="61"/>
       <c r="D26" s="45" t="s">
         <v>76</v>
       </c>
@@ -10116,33 +10208,33 @@
         <v>74</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="H26" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="56"/>
-      <c r="J26" s="59"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="85"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
       <c r="A27" s="124" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="60"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="45" t="s">
         <v>136</v>
-      </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="45" t="s">
-        <v>137</v>
       </c>
       <c r="E27" s="44"/>
       <c r="F27" s="43" t="s">
         <v>74</v>
       </c>
       <c r="G27" s="43"/>
-      <c r="H27" s="58" t="s">
-        <v>138</v>
-      </c>
-      <c r="I27" s="56"/>
-      <c r="J27" s="59"/>
+      <c r="H27" s="84" t="s">
+        <v>137</v>
+      </c>
+      <c r="I27" s="82"/>
+      <c r="J27" s="85"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11122,34 +11214,6 @@
     <row r="1003" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
@@ -11161,6 +11225,34 @@
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11188,16 +11280,16 @@
       <c r="A1" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="94" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="84"/>
-      <c r="F1" s="94" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="84"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -11209,191 +11301,191 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="69" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="69" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="75">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46178</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="79"/>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1">
-      <c r="A3" s="90"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="80"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:16" ht="28.5" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="126" t="s">
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="132" t="s">
         <v>122</v>
       </c>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="86"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:16" ht="21" customHeight="1">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:16" ht="21" customHeight="1">
-      <c r="A7" s="129"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="131"/>
+      <c r="A7" s="127"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="129"/>
     </row>
     <row r="8" spans="1:16" ht="21" customHeight="1">
-      <c r="A8" s="90"/>
-      <c r="B8" s="91"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="132"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="130"/>
     </row>
     <row r="9" spans="1:16" ht="21" customHeight="1">
-      <c r="A9" s="90"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="132"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="130"/>
     </row>
     <row r="10" spans="1:16" ht="21" customHeight="1">
-      <c r="A10" s="90"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="132"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="130"/>
     </row>
     <row r="11" spans="1:16" ht="21" customHeight="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="132"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="130"/>
     </row>
     <row r="12" spans="1:16" ht="21" customHeight="1">
-      <c r="A12" s="90"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="132"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="130"/>
     </row>
     <row r="13" spans="1:16" ht="129.75" customHeight="1">
-      <c r="A13" s="90"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="132"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="130"/>
       <c r="P13" s="48"/>
     </row>
     <row r="14" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="125" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="54"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="63"/>
     </row>
     <row r="15" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53" t="s">
+      <c r="B15" s="60"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="62" t="s">
         <v>121</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="52"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="46" t="s">
         <v>27</v>
       </c>
@@ -11402,11 +11494,11 @@
       </c>
     </row>
     <row r="16" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A16" s="127" t="s">
+      <c r="A16" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="46" t="s">
         <v>29</v>
       </c>
@@ -11419,18 +11511,18 @@
       <c r="G16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="128" t="s">
+      <c r="H16" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="54"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="63"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="134" t="s">
+      <c r="A17" s="133" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="52"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="44" t="s">
         <v>120</v>
       </c>
@@ -11443,18 +11535,18 @@
       <c r="G17" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="54"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="63"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="134" t="s">
+      <c r="A18" s="133" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="44" t="s">
         <v>76</v>
       </c>
@@ -11465,37 +11557,37 @@
         <v>74</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="H18" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="I18" s="51"/>
-      <c r="J18" s="54"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="63"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="134"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
+      <c r="A19" s="133"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="44"/>
       <c r="E19" s="44"/>
       <c r="F19" s="44"/>
       <c r="G19" s="44"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="54"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="63"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A20" s="133"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="57"/>
+      <c r="A20" s="134"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="83"/>
       <c r="D20" s="45"/>
       <c r="E20" s="45"/>
       <c r="F20" s="45"/>
       <c r="G20" s="45"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="59"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="85"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12476,6 +12568,15 @@
     <row r="997" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
@@ -12492,15 +12593,6 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12527,16 +12619,16 @@
       <c r="A1" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="94" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="84"/>
-      <c r="F1" s="94" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="84"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -12548,190 +12640,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="69" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="69" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="75">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46178</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="79"/>
+      <c r="J2" s="65"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="90"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="80"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="126" t="s">
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="132" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="86"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="129"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="131"/>
+      <c r="A7" s="127"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="129"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="90"/>
-      <c r="B8" s="91"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="132"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="130"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="90"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="91"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="132"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="130"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="90"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="132"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="130"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="132"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="130"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="90"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="132"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="130"/>
     </row>
     <row r="13" spans="1:10" ht="141" customHeight="1">
-      <c r="A13" s="90"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="132"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="130"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="125" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="54"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="63"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53" t="s">
+      <c r="B15" s="60"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="62" t="s">
         <v>121</v>
       </c>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="52"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="46" t="s">
         <v>27</v>
       </c>
@@ -12740,11 +12832,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="127" t="s">
+      <c r="A16" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="46" t="s">
         <v>29</v>
       </c>
@@ -12757,18 +12849,18 @@
       <c r="G16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="128" t="s">
+      <c r="H16" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="51"/>
-      <c r="J16" s="54"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="63"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="134" t="s">
+      <c r="A17" s="133" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="52"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="44" t="s">
         <v>120</v>
       </c>
@@ -12781,18 +12873,18 @@
       <c r="G17" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="54"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="63"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="134" t="s">
+      <c r="A18" s="133" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="44" t="s">
         <v>76</v>
       </c>
@@ -12803,25 +12895,25 @@
         <v>74</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="H18" s="53" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="I18" s="51"/>
-      <c r="J18" s="54"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="63"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A19" s="133"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="57"/>
+      <c r="A19" s="134"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="83"/>
       <c r="D19" s="45"/>
       <c r="E19" s="45"/>
       <c r="F19" s="49"/>
       <c r="G19" s="49"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="59"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="85"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13802,16 +13894,6 @@
     <row r="996" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
@@ -13825,6 +13907,16 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13844,7 +13936,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="157" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="110"/>
@@ -13855,14 +13947,14 @@
       <c r="G1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
       <c r="J1" s="118"/>
       <c r="K1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
       <c r="N1" s="118"/>
       <c r="O1" s="117" t="s">
         <v>8</v>
@@ -13875,7 +13967,7 @@
       <c r="S1" s="117" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="148"/>
+      <c r="T1" s="146"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="112"/>
@@ -13885,19 +13977,19 @@
       <c r="E2" s="99"/>
       <c r="F2" s="113"/>
       <c r="G2" s="119"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="153"/>
       <c r="J2" s="120"/>
       <c r="K2" s="119"/>
-      <c r="L2" s="142"/>
-      <c r="M2" s="142"/>
+      <c r="L2" s="153"/>
+      <c r="M2" s="153"/>
       <c r="N2" s="120"/>
       <c r="O2" s="119"/>
       <c r="P2" s="120"/>
       <c r="Q2" s="119"/>
       <c r="R2" s="120"/>
       <c r="S2" s="119"/>
-      <c r="T2" s="143"/>
+      <c r="T2" s="154"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="112"/>
@@ -13919,7 +14011,7 @@
       <c r="Q3" s="121"/>
       <c r="R3" s="113"/>
       <c r="S3" s="121"/>
-      <c r="T3" s="144"/>
+      <c r="T3" s="155"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="114"/>
@@ -13941,36 +14033,36 @@
       <c r="Q4" s="122"/>
       <c r="R4" s="116"/>
       <c r="S4" s="122"/>
-      <c r="T4" s="145"/>
+      <c r="T4" s="156"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="149" t="s">
+      <c r="A5" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="147"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
+      <c r="B5" s="144"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
       <c r="F5" s="118"/>
-      <c r="G5" s="150" t="s">
+      <c r="G5" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="147"/>
-      <c r="M5" s="147"/>
-      <c r="N5" s="147"/>
-      <c r="O5" s="147"/>
-      <c r="P5" s="147"/>
-      <c r="Q5" s="147"/>
-      <c r="R5" s="147"/>
-      <c r="S5" s="147"/>
-      <c r="T5" s="148"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="144"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="144"/>
+      <c r="Q5" s="144"/>
+      <c r="R5" s="144"/>
+      <c r="S5" s="144"/>
+      <c r="T5" s="146"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="151" t="s">
+      <c r="A6" s="147" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="96"/>
@@ -13978,7 +14070,7 @@
       <c r="D6" s="96"/>
       <c r="E6" s="96"/>
       <c r="F6" s="97"/>
-      <c r="G6" s="152" t="s">
+      <c r="G6" s="148" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="96"/>
@@ -13993,10 +14085,10 @@
       <c r="Q6" s="96"/>
       <c r="R6" s="96"/>
       <c r="S6" s="96"/>
-      <c r="T6" s="153"/>
+      <c r="T6" s="149"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="151" t="s">
+      <c r="A7" s="147" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="96"/>
@@ -14004,7 +14096,7 @@
       <c r="D7" s="96"/>
       <c r="E7" s="96"/>
       <c r="F7" s="97"/>
-      <c r="G7" s="152" t="s">
+      <c r="G7" s="148" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="96"/>
@@ -14019,7 +14111,7 @@
       <c r="Q7" s="96"/>
       <c r="R7" s="96"/>
       <c r="S7" s="96"/>
-      <c r="T7" s="153"/>
+      <c r="T7" s="149"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -14218,33 +14310,33 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="151" t="s">
+      <c r="A15" s="147" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="97"/>
-      <c r="C15" s="156" t="s">
+      <c r="C15" s="152" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="97"/>
-      <c r="E15" s="135" t="s">
+      <c r="E15" s="151" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="97"/>
-      <c r="G15" s="135" t="s">
+      <c r="G15" s="151" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="96"/>
       <c r="I15" s="97"/>
-      <c r="J15" s="135" t="s">
+      <c r="J15" s="151" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="97"/>
-      <c r="L15" s="135" t="s">
+      <c r="L15" s="151" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="96"/>
       <c r="N15" s="97"/>
-      <c r="O15" s="135" t="s">
+      <c r="O15" s="151" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="96"/>
@@ -14260,24 +14352,24 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="154">
+      <c r="A16" s="135">
         <v>1</v>
       </c>
       <c r="B16" s="97"/>
-      <c r="C16" s="155" t="s">
+      <c r="C16" s="136" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="97"/>
-      <c r="E16" s="155" t="s">
+      <c r="E16" s="136" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="97"/>
-      <c r="G16" s="136" t="s">
+      <c r="G16" s="150" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="96"/>
       <c r="I16" s="97"/>
-      <c r="J16" s="136" t="s">
+      <c r="J16" s="150" t="s">
         <v>57</v>
       </c>
       <c r="K16" s="97"/>
@@ -14302,24 +14394,24 @@
       <c r="Z16" s="28"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="154">
+      <c r="A17" s="135">
         <v>2</v>
       </c>
       <c r="B17" s="97"/>
-      <c r="C17" s="155" t="s">
+      <c r="C17" s="136" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="97"/>
-      <c r="E17" s="155" t="s">
+      <c r="E17" s="136" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="97"/>
-      <c r="G17" s="136" t="s">
+      <c r="G17" s="150" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="96"/>
       <c r="I17" s="97"/>
-      <c r="J17" s="136" t="s">
+      <c r="J17" s="150" t="s">
         <v>63</v>
       </c>
       <c r="K17" s="97"/>
@@ -14344,16 +14436,16 @@
       <c r="Z17" s="28"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="154"/>
+      <c r="A18" s="135"/>
       <c r="B18" s="97"/>
-      <c r="C18" s="155"/>
+      <c r="C18" s="136"/>
       <c r="D18" s="97"/>
-      <c r="E18" s="155"/>
+      <c r="E18" s="136"/>
       <c r="F18" s="97"/>
-      <c r="G18" s="136"/>
+      <c r="G18" s="150"/>
       <c r="H18" s="96"/>
       <c r="I18" s="97"/>
-      <c r="J18" s="136"/>
+      <c r="J18" s="150"/>
       <c r="K18" s="97"/>
       <c r="L18" s="140"/>
       <c r="M18" s="96"/>
@@ -14372,16 +14464,16 @@
       <c r="Z18" s="28"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="154"/>
+      <c r="A19" s="135"/>
       <c r="B19" s="97"/>
-      <c r="C19" s="155"/>
+      <c r="C19" s="136"/>
       <c r="D19" s="97"/>
-      <c r="E19" s="155"/>
+      <c r="E19" s="136"/>
       <c r="F19" s="97"/>
-      <c r="G19" s="136"/>
+      <c r="G19" s="150"/>
       <c r="H19" s="96"/>
       <c r="I19" s="97"/>
-      <c r="J19" s="136"/>
+      <c r="J19" s="150"/>
       <c r="K19" s="97"/>
       <c r="L19" s="140"/>
       <c r="M19" s="96"/>
@@ -14400,16 +14492,16 @@
       <c r="Z19" s="28"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="154"/>
+      <c r="A20" s="135"/>
       <c r="B20" s="97"/>
-      <c r="C20" s="155"/>
+      <c r="C20" s="136"/>
       <c r="D20" s="97"/>
-      <c r="E20" s="155"/>
+      <c r="E20" s="136"/>
       <c r="F20" s="97"/>
-      <c r="G20" s="136"/>
+      <c r="G20" s="150"/>
       <c r="H20" s="96"/>
       <c r="I20" s="97"/>
-      <c r="J20" s="136"/>
+      <c r="J20" s="150"/>
       <c r="K20" s="97"/>
       <c r="L20" s="140"/>
       <c r="M20" s="96"/>
@@ -14428,16 +14520,16 @@
       <c r="Z20" s="28"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="154"/>
+      <c r="A21" s="135"/>
       <c r="B21" s="97"/>
-      <c r="C21" s="155"/>
+      <c r="C21" s="136"/>
       <c r="D21" s="97"/>
-      <c r="E21" s="155"/>
+      <c r="E21" s="136"/>
       <c r="F21" s="97"/>
-      <c r="G21" s="136"/>
+      <c r="G21" s="150"/>
       <c r="H21" s="96"/>
       <c r="I21" s="97"/>
-      <c r="J21" s="136"/>
+      <c r="J21" s="150"/>
       <c r="K21" s="97"/>
       <c r="L21" s="140"/>
       <c r="M21" s="96"/>
@@ -14456,16 +14548,16 @@
       <c r="Z21" s="28"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="154"/>
+      <c r="A22" s="135"/>
       <c r="B22" s="97"/>
-      <c r="C22" s="155"/>
+      <c r="C22" s="136"/>
       <c r="D22" s="97"/>
-      <c r="E22" s="155"/>
+      <c r="E22" s="136"/>
       <c r="F22" s="97"/>
-      <c r="G22" s="136"/>
+      <c r="G22" s="150"/>
       <c r="H22" s="96"/>
       <c r="I22" s="97"/>
-      <c r="J22" s="136"/>
+      <c r="J22" s="150"/>
       <c r="K22" s="97"/>
       <c r="L22" s="140"/>
       <c r="M22" s="96"/>
@@ -14484,16 +14576,16 @@
       <c r="Z22" s="28"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="154"/>
+      <c r="A23" s="135"/>
       <c r="B23" s="97"/>
-      <c r="C23" s="155"/>
+      <c r="C23" s="136"/>
       <c r="D23" s="97"/>
-      <c r="E23" s="155"/>
+      <c r="E23" s="136"/>
       <c r="F23" s="97"/>
-      <c r="G23" s="136"/>
+      <c r="G23" s="150"/>
       <c r="H23" s="96"/>
       <c r="I23" s="97"/>
-      <c r="J23" s="136"/>
+      <c r="J23" s="150"/>
       <c r="K23" s="97"/>
       <c r="L23" s="140"/>
       <c r="M23" s="96"/>
@@ -14512,16 +14604,16 @@
       <c r="Z23" s="28"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="154"/>
+      <c r="A24" s="135"/>
       <c r="B24" s="97"/>
-      <c r="C24" s="155"/>
+      <c r="C24" s="136"/>
       <c r="D24" s="97"/>
-      <c r="E24" s="155"/>
+      <c r="E24" s="136"/>
       <c r="F24" s="97"/>
-      <c r="G24" s="136"/>
+      <c r="G24" s="150"/>
       <c r="H24" s="96"/>
       <c r="I24" s="97"/>
-      <c r="J24" s="136"/>
+      <c r="J24" s="150"/>
       <c r="K24" s="97"/>
       <c r="L24" s="140"/>
       <c r="M24" s="96"/>
@@ -14540,16 +14632,16 @@
       <c r="Z24" s="28"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="154"/>
+      <c r="A25" s="135"/>
       <c r="B25" s="97"/>
-      <c r="C25" s="155"/>
+      <c r="C25" s="136"/>
       <c r="D25" s="97"/>
-      <c r="E25" s="155"/>
+      <c r="E25" s="136"/>
       <c r="F25" s="97"/>
-      <c r="G25" s="136"/>
+      <c r="G25" s="150"/>
       <c r="H25" s="96"/>
       <c r="I25" s="97"/>
-      <c r="J25" s="136"/>
+      <c r="J25" s="150"/>
       <c r="K25" s="97"/>
       <c r="L25" s="140"/>
       <c r="M25" s="96"/>
@@ -14568,16 +14660,16 @@
       <c r="Z25" s="28"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="154"/>
+      <c r="A26" s="135"/>
       <c r="B26" s="97"/>
-      <c r="C26" s="155"/>
+      <c r="C26" s="136"/>
       <c r="D26" s="97"/>
-      <c r="E26" s="155"/>
+      <c r="E26" s="136"/>
       <c r="F26" s="97"/>
-      <c r="G26" s="136"/>
+      <c r="G26" s="150"/>
       <c r="H26" s="96"/>
       <c r="I26" s="97"/>
-      <c r="J26" s="136"/>
+      <c r="J26" s="150"/>
       <c r="K26" s="97"/>
       <c r="L26" s="140"/>
       <c r="M26" s="96"/>
@@ -14596,16 +14688,16 @@
       <c r="Z26" s="28"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="154"/>
+      <c r="A27" s="135"/>
       <c r="B27" s="97"/>
-      <c r="C27" s="155"/>
+      <c r="C27" s="136"/>
       <c r="D27" s="97"/>
-      <c r="E27" s="155"/>
+      <c r="E27" s="136"/>
       <c r="F27" s="97"/>
-      <c r="G27" s="136"/>
+      <c r="G27" s="150"/>
       <c r="H27" s="96"/>
       <c r="I27" s="97"/>
-      <c r="J27" s="136"/>
+      <c r="J27" s="150"/>
       <c r="K27" s="97"/>
       <c r="L27" s="140"/>
       <c r="M27" s="96"/>
@@ -14624,16 +14716,16 @@
       <c r="Z27" s="28"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="154"/>
+      <c r="A28" s="135"/>
       <c r="B28" s="97"/>
-      <c r="C28" s="155"/>
+      <c r="C28" s="136"/>
       <c r="D28" s="97"/>
-      <c r="E28" s="155"/>
+      <c r="E28" s="136"/>
       <c r="F28" s="97"/>
-      <c r="G28" s="136"/>
+      <c r="G28" s="150"/>
       <c r="H28" s="96"/>
       <c r="I28" s="97"/>
-      <c r="J28" s="136"/>
+      <c r="J28" s="150"/>
       <c r="K28" s="97"/>
       <c r="L28" s="140"/>
       <c r="M28" s="96"/>
@@ -14652,16 +14744,16 @@
       <c r="Z28" s="28"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="154"/>
+      <c r="A29" s="135"/>
       <c r="B29" s="97"/>
-      <c r="C29" s="155"/>
+      <c r="C29" s="136"/>
       <c r="D29" s="97"/>
-      <c r="E29" s="155"/>
+      <c r="E29" s="136"/>
       <c r="F29" s="97"/>
-      <c r="G29" s="136"/>
+      <c r="G29" s="150"/>
       <c r="H29" s="96"/>
       <c r="I29" s="97"/>
-      <c r="J29" s="136"/>
+      <c r="J29" s="150"/>
       <c r="K29" s="97"/>
       <c r="L29" s="140"/>
       <c r="M29" s="96"/>
@@ -14680,16 +14772,16 @@
       <c r="Z29" s="28"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="154"/>
+      <c r="A30" s="135"/>
       <c r="B30" s="97"/>
-      <c r="C30" s="155"/>
+      <c r="C30" s="136"/>
       <c r="D30" s="97"/>
-      <c r="E30" s="155"/>
+      <c r="E30" s="136"/>
       <c r="F30" s="97"/>
-      <c r="G30" s="136"/>
+      <c r="G30" s="150"/>
       <c r="H30" s="96"/>
       <c r="I30" s="97"/>
-      <c r="J30" s="136"/>
+      <c r="J30" s="150"/>
       <c r="K30" s="97"/>
       <c r="L30" s="140"/>
       <c r="M30" s="96"/>
@@ -14708,23 +14800,23 @@
       <c r="Z30" s="28"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="157"/>
-      <c r="B31" s="139"/>
-      <c r="C31" s="158"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="137"/>
-      <c r="H31" s="138"/>
-      <c r="I31" s="139"/>
-      <c r="J31" s="137"/>
-      <c r="K31" s="139"/>
+      <c r="A31" s="137"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="158"/>
+      <c r="H31" s="142"/>
+      <c r="I31" s="138"/>
+      <c r="J31" s="158"/>
+      <c r="K31" s="138"/>
       <c r="L31" s="141"/>
-      <c r="M31" s="138"/>
-      <c r="N31" s="139"/>
+      <c r="M31" s="142"/>
+      <c r="N31" s="138"/>
       <c r="O31" s="141"/>
-      <c r="P31" s="138"/>
-      <c r="Q31" s="139"/>
+      <c r="P31" s="142"/>
+      <c r="Q31" s="138"/>
       <c r="R31" s="29"/>
       <c r="S31" s="29"/>
       <c r="T31" s="30"/>
@@ -15722,6 +15814,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -15746,118 +15950,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/タスク登録機能_詳細設計書.xlsx
+++ b/document/タスク登録機能_詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7CF31E-9062-49BC-8D41-01DAFE0400EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DD3A23-D576-468D-A8D6-B227FF40A961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -229,16 +229,6 @@
   <si>
     <t>エラー画面へ遷移する
 エラーの原因がユーザ名が未入力である旨通知する</t>
-  </si>
-  <si>
-    <t>データーベースに新規タスクが登録される。</t>
-    <rPh sb="8" eb="10">
-      <t>シンキ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>従業員</t>
@@ -683,49 +673,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>E1：データベース接続または登録処理に失敗した場合
-E1-1. 基本フロー6で、システムはデータベースへの登録に失敗する。
-E1-2. システムはタスク情報を登録せず、タスク登録画面を再表示する。
-E1-3. システムは「現在タスクの登録ができません。しばらくしてから再度お試しください。」というエラーメッセージを表示する。
-E1-4. 従業員は時間を置いてから再度登録を試行する。</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1. 従業員はメニュー画面より「タスク登録」ボタンを押下し、タスク登録画面へ遷移する。
-2. システムはタスク登録画面を表示する。
-3. 従業員は登録項目を入力する。
-  ・必須項目：タスク名、カテゴリ情報、担当者情報、ステータス情報
-  ・任意項目：期限、メモ　※期限を入力する場合は、本日以降の日付を指定する。
-4. 従業員は「登録」ボタンを押下する。
-5. システムは下記の入力内容をチェックする。
-   ・必須項目が入力されていること
-   ・期限が過去日付ではないこと
-6. システムは入力されたタスク情報をデータベースに登録する。
-7. システムは登録完了画面を表示する。
-8. 従業員は「メニュー画面へ」ボタンを押下する。
-9. システムはメニュー画面を表示する。</t>
-    <rPh sb="187" eb="189">
-      <t>カキ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>従業員がログインに成功している状態であること。</t>
-    <rPh sb="0" eb="2">
-      <t>ジュウギョウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>イン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスクの期限をカレンダーから入力できるフォーム。過去日付は選択不可。</t>
     <rPh sb="4" eb="6">
       <t>キゲン</t>
@@ -793,22 +740,166 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>A1：必須項目に未入力がある場合
-A1-1. 基本フロー5で、システムは必須項目の未入力を検出する。
+    <t>データベースに新規タスクが登録される。システムは登録完了画面を表示する。</t>
+    <rPh sb="7" eb="9">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>トウロクカンリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>従業員がログインに成功している状態であること。
+カテゴリマスタにカテゴリ情報（カテゴリ名）が登録されていること。
+ユーザマスタに従業員のユーザ情報（ユーザー名）が登録されていること。
+ステータスマスタにステータス情報（ステータス名）が登録されていること。</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウギョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="64" eb="67">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="114" eb="115">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.従業員はメニュー画面より「タスク登録」ボタンを押下し、タスク登録画面へ遷移する。
+2.システムはタスク登録画面の下記の項目におけるプルダウン用のマスタ情報を取得する。
+  ・カテゴリマスタ
+　・ユーザマスタ
+　・ステータスマスタ
+3. システムはタスク登録画面を表示する。
+4. 従業員は登録項目を入力する。
+  ・必須項目：タスク名、カテゴリ情報、担当者情報、ステータス情報
+  ・任意項目：期限、メモ　※期限を入力する場合は、本日以降の日付を指定する。
+5. 従業員は「登録」ボタンを押下する。
+6. システムは下記の入力内容をチェックする。
+   ・必須項目が入力されていること
+   ・期限が過去日付ではないこと
+   ・タスク名およびメモの文字数が、項目ごとに定められた上限文字数以内であること
+7. システムは入力されたタスク情報をデータベースに登録する。
+8. システムは登録完了画面を表示する。
+9. 従業員は「メニュー画面へ」ボタンを押下する。
+10. システムはメニュー画面を表示する。</t>
+    <rPh sb="53" eb="57">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="260" eb="262">
+      <t>カキ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>E1：データベース接続または登録処理に失敗した場合
+E1-1. 基本フロー7で、システムはデータベースへの登録に失敗する。
+E1-2. システムはタスク情報を登録せず、タスク登録失敗画面を表示する。
+E1-3.従業員はエラー画面に従い、「メニュー画面へ」ボタンを押下し基本フロー１から再試行する。</t>
+    <rPh sb="89" eb="91">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="105" eb="108">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>シタガ</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="142" eb="145">
+      <t>サイシコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>A1:必須項目に未入力がある場合
+A1-1. 基本フロー6で、システムは必須項目の未入力を検出する。
 A1-2. システムはエラーメッセージを表示したタスク登録画面を再表示する。
-A1-3. 従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。
-A2：期限に過去日付が入力された場合
-A2-1. 基本フロー5で、システムは期限に過去日付が入力されていることを検出する。
+A1-3. 従業員はエラーメッセージに従い入力内容を修正し、基本フロー4から再試行する。
+A2:期限に過去日付が入力された場合
+A2-1. 基本フロー6で、システムは期限に過去日付が入力されていることを検出する。
 A2-2. システムは「期限に過去日付は指定できません。」というエラーメッセージを表示したタスク登録画面を再表示し、登録処理を行わない。
-A2-3. 従業員は期限を当日以降の日付に修正し、基本フロー3から再試行する。
+A2-3. 従業員は期限を当日以降の日付に修正し、基本フロー4から再試行する。
 A3:タスク名の文字数が50文字を超過する場合
-A3-1:基本フロー5で、システムはタスク名の文字数に50文字を超える入力されていることを検出する。
-A3-2:システムは「タスク名は50文字以内で入力してください。」というエラーメッセージを表示したタスク登録画面を再表示する。
-A3-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。
+A3-1.基本フロー6で、システムはタスク名の文字数が50文字を超えていることを検出する。
+A3-2.システムは「タスク名は50文字以内で入力してください。」というエラーメッセージを表示したタスク登録画面を再表示する。
+A3-3.従業員はエラーメッセージに従い入力内容を修正し、基本フロー4から再試行する。
 A4:メモの文字数が100文字を超過する場合
-A4-1:基本フロー5で、システムはメモの文字数に100文字を超える入力されていることを検出する。
-A4-2:システムは「メモは100文字以内で入力してください。」というエラーメッセージを表示したタスク登録画面を再表示する。
-A4-3:従業員はエラーメッセージに従い入力内容を修正し、基本フロー3から再試行する。</t>
+A4-1.基本フロー6で、システムはメモの文字数が100文字を超えていることを検出する。
+A4-2.システムは「メモは100文字以内で入力してください。」というエラーメッセージを表示したタスク登録画面を再表示する。
+A4-3.従業員はエラーメッセージに従い入力内容を修正し、基本フロー4から再試行する。</t>
     <rPh sb="314" eb="315">
       <t>メイ</t>
     </rPh>
@@ -827,70 +918,61 @@
     <rPh sb="353" eb="354">
       <t>メイ</t>
     </rPh>
-    <rPh sb="355" eb="358">
+    <rPh sb="392" eb="393">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="396" eb="398">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="398" eb="400">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="401" eb="403">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="423" eb="425">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="430" eb="432">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="432" eb="434">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="435" eb="438">
+      <t>サイヒョウジ</t>
+    </rPh>
+    <rPh sb="447" eb="450">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="460" eb="461">
+      <t>シタガ</t>
+    </rPh>
+    <rPh sb="462" eb="464">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="464" eb="466">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="467" eb="469">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="471" eb="473">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="479" eb="482">
+      <t>サイシコウ</t>
+    </rPh>
+    <rPh sb="493" eb="496">
       <t>モジスウ</t>
     </rPh>
-    <rPh sb="361" eb="363">
+    <rPh sb="500" eb="502">
       <t>モジ</t>
     </rPh>
-    <rPh sb="364" eb="365">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="397" eb="398">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="401" eb="403">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="403" eb="405">
-      <t>イナイ</t>
-    </rPh>
-    <rPh sb="406" eb="408">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="428" eb="430">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="435" eb="437">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="437" eb="439">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="440" eb="443">
-      <t>サイヒョウジ</t>
-    </rPh>
-    <rPh sb="452" eb="455">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="465" eb="466">
-      <t>シタガ</t>
-    </rPh>
-    <rPh sb="467" eb="469">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="469" eb="471">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="472" eb="474">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="476" eb="478">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="484" eb="487">
-      <t>サイシコウ</t>
-    </rPh>
-    <rPh sb="498" eb="501">
-      <t>モジスウ</t>
-    </rPh>
-    <rPh sb="505" eb="507">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="508" eb="510">
+    <rPh sb="503" eb="505">
       <t>チョウカ</t>
     </rPh>
-    <rPh sb="512" eb="514">
+    <rPh sb="507" eb="509">
       <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -1819,6 +1901,63 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1844,21 +1983,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1911,48 +2035,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2044,12 +2126,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2068,65 +2144,38 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2143,8 +2192,41 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2166,20 +2248,25 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:colOff>56029</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="12946426" cy="5295900"/>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>183216</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>155762</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{390B2F0D-59D2-46DF-8A39-14DB780111F7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09EAFA31-D9DD-605F-2799-190F695543CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2201,8 +2288,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="971550"/>
-          <a:ext cx="12946426" cy="5295900"/>
+          <a:off x="56029" y="1053353"/>
+          <a:ext cx="15344775" cy="4705350"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2210,7 +2297,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5661,19 +5748,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="80" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="80" t="s">
+      <c r="E1" s="84"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="84"/>
       <c r="H1" s="33" t="s">
         <v>8</v>
       </c>
@@ -5685,192 +5772,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="50" t="s">
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="56">
+      <c r="E2" s="70"/>
+      <c r="F2" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="70"/>
+      <c r="H2" s="75">
         <v>46189</v>
       </c>
-      <c r="I2" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="65"/>
+      <c r="I2" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="79"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="66"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="80"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="78"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="67"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="81"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="71" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="72"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="85" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="86"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="63"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="62" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="63"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="59" t="s">
+      <c r="B7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="54"/>
+    </row>
+    <row r="8" spans="1:10" ht="73.5" customHeight="1">
+      <c r="A8" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="60"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="62" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="63"/>
-    </row>
-    <row r="9" spans="1:10" ht="203.25" customHeight="1">
-      <c r="A9" s="86" t="s">
+      <c r="B8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="64" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="54"/>
+    </row>
+    <row r="9" spans="1:10" ht="258.75" customHeight="1">
+      <c r="A9" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="89" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="61"/>
-      <c r="D9" s="90" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="63"/>
+      <c r="B9" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="54"/>
     </row>
     <row r="10" spans="1:10" ht="289.5" customHeight="1">
-      <c r="A10" s="87"/>
-      <c r="B10" s="89" t="s">
+      <c r="A10" s="61"/>
+      <c r="B10" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="91" t="s">
+      <c r="C10" s="52"/>
+      <c r="D10" s="65" t="s">
         <v>138</v>
       </c>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="93"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="84" customHeight="1">
-      <c r="A11" s="88"/>
-      <c r="B11" s="89" t="s">
+      <c r="A11" s="62"/>
+      <c r="B11" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="92"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="93"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="68" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="59" t="s">
+      <c r="A12" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="60"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="63"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="54"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="82"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="85"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="59"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6861,17 +6948,6 @@
     <row r="1000" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A7:C7"/>
@@ -6888,6 +6964,17 @@
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="D2:E4"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -8323,16 +8410,16 @@
       <c r="A1" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="80" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="80" t="s">
+      <c r="E1" s="84"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="84"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -8344,48 +8431,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="50" t="s">
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="56">
+      <c r="E2" s="70"/>
+      <c r="F2" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="70"/>
+      <c r="H2" s="75">
         <v>46181</v>
       </c>
-      <c r="I2" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="65"/>
+      <c r="I2" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="79"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="66"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="80"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="78"/>
-      <c r="B4" s="79"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="67"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="81"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="41"/>
@@ -9743,16 +9830,16 @@
       <c r="A1" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="80" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="80" t="s">
+      <c r="E1" s="84"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="84"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -9764,203 +9851,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="50" t="s">
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="56">
+      <c r="E2" s="70"/>
+      <c r="F2" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="70"/>
+      <c r="H2" s="75">
         <v>46178</v>
       </c>
-      <c r="I2" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="65"/>
+      <c r="I2" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="79"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="66"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="80"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="76"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="132" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="72"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="130" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="86"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="125" t="s">
+      <c r="A6" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="63"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="127"/>
-      <c r="B7" s="128"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="129"/>
+      <c r="A7" s="125"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="76"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="130"/>
+      <c r="A8" s="90"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="128"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="76"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="130"/>
+      <c r="A9" s="90"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="128"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="76"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="130"/>
+      <c r="A10" s="90"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="128"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="76"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="130"/>
+      <c r="A11" s="90"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="128"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="76"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="130"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="128"/>
     </row>
     <row r="13" spans="1:10" ht="165.75" customHeight="1">
-      <c r="A13" s="76"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="130"/>
+      <c r="A13" s="90"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="128"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="125" t="s">
+      <c r="A14" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="63"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="62" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="61"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="52"/>
       <c r="I15" s="46" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="125" t="s">
+      <c r="A16" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="61"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="46" t="s">
         <v>29</v>
       </c>
@@ -9973,268 +10060,268 @@
       <c r="G16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="126" t="s">
+      <c r="H16" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="60"/>
-      <c r="J16" s="63"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
       <c r="A17" s="124" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="61"/>
+        <v>112</v>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="44" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="I17" s="60"/>
-      <c r="J17" s="63"/>
+        <v>73</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="I17" s="51"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="124" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" s="60"/>
-      <c r="C18" s="61"/>
+        <v>108</v>
+      </c>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F18" s="44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="I18" s="60"/>
-      <c r="J18" s="63"/>
+        <v>73</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="51"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="124" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" s="60"/>
-      <c r="C19" s="61"/>
+        <v>104</v>
+      </c>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E19" s="44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F19" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G19" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>102</v>
-      </c>
-      <c r="I19" s="60"/>
-      <c r="J19" s="63"/>
+        <v>126</v>
+      </c>
+      <c r="H19" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19" s="51"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="124" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="61"/>
+        <v>100</v>
+      </c>
+      <c r="B20" s="51"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G20" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="H20" s="62" t="s">
-        <v>128</v>
-      </c>
-      <c r="I20" s="60"/>
-      <c r="J20" s="63"/>
+        <v>73</v>
+      </c>
+      <c r="H20" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" s="51"/>
+      <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
       <c r="A21" s="124" t="s">
-        <v>97</v>
-      </c>
-      <c r="B21" s="60"/>
-      <c r="C21" s="61"/>
+        <v>96</v>
+      </c>
+      <c r="B21" s="51"/>
+      <c r="C21" s="52"/>
       <c r="D21" s="44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>132</v>
-      </c>
-      <c r="H21" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="I21" s="60"/>
-      <c r="J21" s="63"/>
+        <v>128</v>
+      </c>
+      <c r="H21" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="51"/>
+      <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
       <c r="A22" s="124" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="61"/>
+        <v>92</v>
+      </c>
+      <c r="B22" s="51"/>
+      <c r="C22" s="52"/>
       <c r="D22" s="44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="I22" s="60"/>
-      <c r="J22" s="63"/>
+      <c r="H22" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="I22" s="51"/>
+      <c r="J22" s="54"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
       <c r="A23" s="124" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="60"/>
-      <c r="C23" s="61"/>
+        <v>87</v>
+      </c>
+      <c r="B23" s="51"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G23" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="I23" s="60"/>
-      <c r="J23" s="63"/>
+        <v>73</v>
+      </c>
+      <c r="H23" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="I23" s="51"/>
+      <c r="J23" s="54"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
       <c r="A24" s="124" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="60"/>
-      <c r="C24" s="61"/>
+        <v>82</v>
+      </c>
+      <c r="B24" s="51"/>
+      <c r="C24" s="52"/>
       <c r="D24" s="44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F24" s="43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="H24" s="62" t="s">
-        <v>81</v>
-      </c>
-      <c r="I24" s="60"/>
-      <c r="J24" s="63"/>
+        <v>130</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="51"/>
+      <c r="J24" s="54"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
       <c r="A25" s="124" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="60"/>
-      <c r="C25" s="61"/>
+        <v>79</v>
+      </c>
+      <c r="B25" s="51"/>
+      <c r="C25" s="52"/>
       <c r="D25" s="44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F25" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" s="62" t="s">
-        <v>78</v>
-      </c>
-      <c r="I25" s="60"/>
-      <c r="J25" s="63"/>
+        <v>73</v>
+      </c>
+      <c r="H25" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="51"/>
+      <c r="J25" s="54"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A26" s="124" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="61"/>
+        <v>76</v>
+      </c>
+      <c r="B26" s="51"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F26" s="43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="H26" s="84" t="s">
-        <v>73</v>
-      </c>
-      <c r="I26" s="82"/>
-      <c r="J26" s="85"/>
+        <v>125</v>
+      </c>
+      <c r="H26" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="I26" s="56"/>
+      <c r="J26" s="59"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
       <c r="A27" s="124" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="61"/>
+        <v>131</v>
+      </c>
+      <c r="B27" s="51"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="45" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E27" s="44"/>
       <c r="F27" s="43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G27" s="43"/>
-      <c r="H27" s="84" t="s">
-        <v>137</v>
-      </c>
-      <c r="I27" s="82"/>
-      <c r="J27" s="85"/>
+      <c r="H27" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="I27" s="56"/>
+      <c r="J27" s="59"/>
     </row>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11214,29 +11301,6 @@
     <row r="1003" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="H27:J27"/>
     <mergeCell ref="A16:C16"/>
@@ -11253,6 +11317,29 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="H25:J25"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11280,16 +11367,16 @@
       <c r="A1" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="80" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="80" t="s">
+      <c r="E1" s="84"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="84"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -11301,204 +11388,204 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="50" t="s">
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="56">
+      <c r="E2" s="70"/>
+      <c r="F2" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="70"/>
+      <c r="H2" s="75">
         <v>46178</v>
       </c>
-      <c r="I2" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="65"/>
+      <c r="I2" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="79"/>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="66"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="80"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="76"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:16" ht="28.5" customHeight="1">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="132" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="72"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="86"/>
     </row>
     <row r="6" spans="1:16" ht="21" customHeight="1">
-      <c r="A6" s="125" t="s">
+      <c r="A6" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="63"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:16" ht="21" customHeight="1">
-      <c r="A7" s="127"/>
-      <c r="B7" s="128"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="129"/>
+      <c r="A7" s="125"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
     </row>
     <row r="8" spans="1:16" ht="21" customHeight="1">
-      <c r="A8" s="76"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="130"/>
+      <c r="A8" s="90"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="128"/>
     </row>
     <row r="9" spans="1:16" ht="21" customHeight="1">
-      <c r="A9" s="76"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="130"/>
+      <c r="A9" s="90"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="128"/>
     </row>
     <row r="10" spans="1:16" ht="21" customHeight="1">
-      <c r="A10" s="76"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="130"/>
+      <c r="A10" s="90"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="128"/>
     </row>
     <row r="11" spans="1:16" ht="21" customHeight="1">
-      <c r="A11" s="76"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="130"/>
+      <c r="A11" s="90"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="128"/>
     </row>
     <row r="12" spans="1:16" ht="21" customHeight="1">
-      <c r="A12" s="76"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="130"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="128"/>
     </row>
     <row r="13" spans="1:16" ht="129.75" customHeight="1">
-      <c r="A13" s="76"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="130"/>
+      <c r="A13" s="90"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="128"/>
       <c r="P13" s="48"/>
     </row>
     <row r="14" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A14" s="125" t="s">
+      <c r="A14" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="63"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="62" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="61"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="52"/>
       <c r="I15" s="46" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="19.5" customHeight="1">
-      <c r="A16" s="125" t="s">
+      <c r="A16" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="61"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="46" t="s">
         <v>29</v>
       </c>
@@ -11511,83 +11598,83 @@
       <c r="G16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="126" t="s">
+      <c r="H16" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="60"/>
-      <c r="J16" s="63"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="133" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="61"/>
+      <c r="A17" s="134" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="60"/>
-      <c r="J17" s="63"/>
+        <v>73</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="51"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="133" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" s="60"/>
-      <c r="C18" s="61"/>
+      <c r="A18" s="134" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="I18" s="60"/>
-      <c r="J18" s="63"/>
+        <v>125</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="51"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="133"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="61"/>
+      <c r="A19" s="134"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="44"/>
       <c r="E19" s="44"/>
       <c r="F19" s="44"/>
       <c r="G19" s="44"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="63"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A20" s="134"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="83"/>
+      <c r="A20" s="133"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="57"/>
       <c r="D20" s="45"/>
       <c r="E20" s="45"/>
       <c r="F20" s="45"/>
       <c r="G20" s="45"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="85"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="59"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12568,15 +12655,6 @@
     <row r="997" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
@@ -12593,6 +12671,15 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12619,16 +12706,16 @@
       <c r="A1" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="80" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="80" t="s">
+      <c r="E1" s="84"/>
+      <c r="F1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="84"/>
       <c r="H1" s="34" t="s">
         <v>8</v>
       </c>
@@ -12640,203 +12727,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="50" t="s">
+      <c r="A2" s="90"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="56">
+      <c r="E2" s="70"/>
+      <c r="F2" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="70"/>
+      <c r="H2" s="75">
         <v>46178</v>
       </c>
-      <c r="I2" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="65"/>
+      <c r="I2" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="79"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="66"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="80"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="76"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="66"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="132" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="72"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="130" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="86"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="125" t="s">
+      <c r="A6" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="63"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="127"/>
-      <c r="B7" s="128"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="129"/>
+      <c r="A7" s="125"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="127"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="76"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="130"/>
+      <c r="A8" s="90"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="128"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="76"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="130"/>
+      <c r="A9" s="90"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="91"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="128"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="76"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="130"/>
+      <c r="A10" s="90"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="91"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="128"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="76"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="130"/>
+      <c r="A11" s="90"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="128"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="76"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="130"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="128"/>
     </row>
     <row r="13" spans="1:10" ht="141" customHeight="1">
-      <c r="A13" s="76"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="130"/>
+      <c r="A13" s="90"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="128"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="125" t="s">
+      <c r="A14" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="63"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="125" t="s">
+      <c r="A15" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="62" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="61"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="52"/>
       <c r="I15" s="46" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="125" t="s">
+      <c r="A16" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="61"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
       <c r="D16" s="46" t="s">
         <v>29</v>
       </c>
@@ -12849,71 +12936,71 @@
       <c r="G16" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="126" t="s">
+      <c r="H16" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="60"/>
-      <c r="J16" s="63"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="133" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="61"/>
+      <c r="A17" s="134" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="52"/>
       <c r="D17" s="44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E17" s="44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="60"/>
-      <c r="J17" s="63"/>
+        <v>73</v>
+      </c>
+      <c r="H17" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="51"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="133" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" s="60"/>
-      <c r="C18" s="61"/>
+      <c r="A18" s="134" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" s="44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="I18" s="60"/>
-      <c r="J18" s="63"/>
+        <v>125</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="51"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A19" s="134"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="83"/>
+      <c r="A19" s="133"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="57"/>
       <c r="D19" s="45"/>
       <c r="E19" s="45"/>
       <c r="F19" s="49"/>
       <c r="G19" s="49"/>
-      <c r="H19" s="84"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="85"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="59"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13894,6 +13981,16 @@
     <row r="996" s="31" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
@@ -13907,16 +14004,6 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13936,7 +14023,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="146" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="110"/>
@@ -13947,14 +14034,14 @@
       <c r="G1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
       <c r="J1" s="118"/>
       <c r="K1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
       <c r="N1" s="118"/>
       <c r="O1" s="117" t="s">
         <v>8</v>
@@ -13967,7 +14054,7 @@
       <c r="S1" s="117" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="146"/>
+      <c r="T1" s="148"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="112"/>
@@ -13977,19 +14064,19 @@
       <c r="E2" s="99"/>
       <c r="F2" s="113"/>
       <c r="G2" s="119"/>
-      <c r="H2" s="153"/>
-      <c r="I2" s="153"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
       <c r="J2" s="120"/>
       <c r="K2" s="119"/>
-      <c r="L2" s="153"/>
-      <c r="M2" s="153"/>
+      <c r="L2" s="142"/>
+      <c r="M2" s="142"/>
       <c r="N2" s="120"/>
       <c r="O2" s="119"/>
       <c r="P2" s="120"/>
       <c r="Q2" s="119"/>
       <c r="R2" s="120"/>
       <c r="S2" s="119"/>
-      <c r="T2" s="154"/>
+      <c r="T2" s="143"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="112"/>
@@ -14011,7 +14098,7 @@
       <c r="Q3" s="121"/>
       <c r="R3" s="113"/>
       <c r="S3" s="121"/>
-      <c r="T3" s="155"/>
+      <c r="T3" s="144"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="114"/>
@@ -14033,36 +14120,36 @@
       <c r="Q4" s="122"/>
       <c r="R4" s="116"/>
       <c r="S4" s="122"/>
-      <c r="T4" s="156"/>
+      <c r="T4" s="145"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="143" t="s">
+      <c r="A5" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="144"/>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="144"/>
+      <c r="B5" s="147"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="147"/>
       <c r="F5" s="118"/>
-      <c r="G5" s="145" t="s">
+      <c r="G5" s="150" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="144"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="144"/>
-      <c r="K5" s="144"/>
-      <c r="L5" s="144"/>
-      <c r="M5" s="144"/>
-      <c r="N5" s="144"/>
-      <c r="O5" s="144"/>
-      <c r="P5" s="144"/>
-      <c r="Q5" s="144"/>
-      <c r="R5" s="144"/>
-      <c r="S5" s="144"/>
-      <c r="T5" s="146"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="147"/>
+      <c r="L5" s="147"/>
+      <c r="M5" s="147"/>
+      <c r="N5" s="147"/>
+      <c r="O5" s="147"/>
+      <c r="P5" s="147"/>
+      <c r="Q5" s="147"/>
+      <c r="R5" s="147"/>
+      <c r="S5" s="147"/>
+      <c r="T5" s="148"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="147" t="s">
+      <c r="A6" s="151" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="96"/>
@@ -14070,7 +14157,7 @@
       <c r="D6" s="96"/>
       <c r="E6" s="96"/>
       <c r="F6" s="97"/>
-      <c r="G6" s="148" t="s">
+      <c r="G6" s="152" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="96"/>
@@ -14085,10 +14172,10 @@
       <c r="Q6" s="96"/>
       <c r="R6" s="96"/>
       <c r="S6" s="96"/>
-      <c r="T6" s="149"/>
+      <c r="T6" s="153"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="147" t="s">
+      <c r="A7" s="151" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="96"/>
@@ -14096,7 +14183,7 @@
       <c r="D7" s="96"/>
       <c r="E7" s="96"/>
       <c r="F7" s="97"/>
-      <c r="G7" s="148" t="s">
+      <c r="G7" s="152" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="96"/>
@@ -14111,7 +14198,7 @@
       <c r="Q7" s="96"/>
       <c r="R7" s="96"/>
       <c r="S7" s="96"/>
-      <c r="T7" s="149"/>
+      <c r="T7" s="153"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -14310,33 +14397,33 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="147" t="s">
+      <c r="A15" s="151" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="97"/>
-      <c r="C15" s="152" t="s">
+      <c r="C15" s="156" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="97"/>
-      <c r="E15" s="151" t="s">
+      <c r="E15" s="135" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="97"/>
-      <c r="G15" s="151" t="s">
+      <c r="G15" s="135" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="96"/>
       <c r="I15" s="97"/>
-      <c r="J15" s="151" t="s">
+      <c r="J15" s="135" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="97"/>
-      <c r="L15" s="151" t="s">
+      <c r="L15" s="135" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="96"/>
       <c r="N15" s="97"/>
-      <c r="O15" s="151" t="s">
+      <c r="O15" s="135" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="96"/>
@@ -14352,24 +14439,24 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="135">
+      <c r="A16" s="154">
         <v>1</v>
       </c>
       <c r="B16" s="97"/>
-      <c r="C16" s="136" t="s">
+      <c r="C16" s="155" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="97"/>
-      <c r="E16" s="136" t="s">
+      <c r="E16" s="155" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="97"/>
-      <c r="G16" s="150" t="s">
+      <c r="G16" s="136" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="96"/>
       <c r="I16" s="97"/>
-      <c r="J16" s="150" t="s">
+      <c r="J16" s="136" t="s">
         <v>57</v>
       </c>
       <c r="K16" s="97"/>
@@ -14394,24 +14481,24 @@
       <c r="Z16" s="28"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="135">
+      <c r="A17" s="154">
         <v>2</v>
       </c>
       <c r="B17" s="97"/>
-      <c r="C17" s="136" t="s">
+      <c r="C17" s="155" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="97"/>
-      <c r="E17" s="136" t="s">
+      <c r="E17" s="155" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="97"/>
-      <c r="G17" s="150" t="s">
+      <c r="G17" s="136" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="96"/>
       <c r="I17" s="97"/>
-      <c r="J17" s="150" t="s">
+      <c r="J17" s="136" t="s">
         <v>63</v>
       </c>
       <c r="K17" s="97"/>
@@ -14436,16 +14523,16 @@
       <c r="Z17" s="28"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="135"/>
+      <c r="A18" s="154"/>
       <c r="B18" s="97"/>
-      <c r="C18" s="136"/>
+      <c r="C18" s="155"/>
       <c r="D18" s="97"/>
-      <c r="E18" s="136"/>
+      <c r="E18" s="155"/>
       <c r="F18" s="97"/>
-      <c r="G18" s="150"/>
+      <c r="G18" s="136"/>
       <c r="H18" s="96"/>
       <c r="I18" s="97"/>
-      <c r="J18" s="150"/>
+      <c r="J18" s="136"/>
       <c r="K18" s="97"/>
       <c r="L18" s="140"/>
       <c r="M18" s="96"/>
@@ -14464,16 +14551,16 @@
       <c r="Z18" s="28"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="135"/>
+      <c r="A19" s="154"/>
       <c r="B19" s="97"/>
-      <c r="C19" s="136"/>
+      <c r="C19" s="155"/>
       <c r="D19" s="97"/>
-      <c r="E19" s="136"/>
+      <c r="E19" s="155"/>
       <c r="F19" s="97"/>
-      <c r="G19" s="150"/>
+      <c r="G19" s="136"/>
       <c r="H19" s="96"/>
       <c r="I19" s="97"/>
-      <c r="J19" s="150"/>
+      <c r="J19" s="136"/>
       <c r="K19" s="97"/>
       <c r="L19" s="140"/>
       <c r="M19" s="96"/>
@@ -14492,16 +14579,16 @@
       <c r="Z19" s="28"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="135"/>
+      <c r="A20" s="154"/>
       <c r="B20" s="97"/>
-      <c r="C20" s="136"/>
+      <c r="C20" s="155"/>
       <c r="D20" s="97"/>
-      <c r="E20" s="136"/>
+      <c r="E20" s="155"/>
       <c r="F20" s="97"/>
-      <c r="G20" s="150"/>
+      <c r="G20" s="136"/>
       <c r="H20" s="96"/>
       <c r="I20" s="97"/>
-      <c r="J20" s="150"/>
+      <c r="J20" s="136"/>
       <c r="K20" s="97"/>
       <c r="L20" s="140"/>
       <c r="M20" s="96"/>
@@ -14520,16 +14607,16 @@
       <c r="Z20" s="28"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="135"/>
+      <c r="A21" s="154"/>
       <c r="B21" s="97"/>
-      <c r="C21" s="136"/>
+      <c r="C21" s="155"/>
       <c r="D21" s="97"/>
-      <c r="E21" s="136"/>
+      <c r="E21" s="155"/>
       <c r="F21" s="97"/>
-      <c r="G21" s="150"/>
+      <c r="G21" s="136"/>
       <c r="H21" s="96"/>
       <c r="I21" s="97"/>
-      <c r="J21" s="150"/>
+      <c r="J21" s="136"/>
       <c r="K21" s="97"/>
       <c r="L21" s="140"/>
       <c r="M21" s="96"/>
@@ -14548,16 +14635,16 @@
       <c r="Z21" s="28"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="135"/>
+      <c r="A22" s="154"/>
       <c r="B22" s="97"/>
-      <c r="C22" s="136"/>
+      <c r="C22" s="155"/>
       <c r="D22" s="97"/>
-      <c r="E22" s="136"/>
+      <c r="E22" s="155"/>
       <c r="F22" s="97"/>
-      <c r="G22" s="150"/>
+      <c r="G22" s="136"/>
       <c r="H22" s="96"/>
       <c r="I22" s="97"/>
-      <c r="J22" s="150"/>
+      <c r="J22" s="136"/>
       <c r="K22" s="97"/>
       <c r="L22" s="140"/>
       <c r="M22" s="96"/>
@@ -14576,16 +14663,16 @@
       <c r="Z22" s="28"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="135"/>
+      <c r="A23" s="154"/>
       <c r="B23" s="97"/>
-      <c r="C23" s="136"/>
+      <c r="C23" s="155"/>
       <c r="D23" s="97"/>
-      <c r="E23" s="136"/>
+      <c r="E23" s="155"/>
       <c r="F23" s="97"/>
-      <c r="G23" s="150"/>
+      <c r="G23" s="136"/>
       <c r="H23" s="96"/>
       <c r="I23" s="97"/>
-      <c r="J23" s="150"/>
+      <c r="J23" s="136"/>
       <c r="K23" s="97"/>
       <c r="L23" s="140"/>
       <c r="M23" s="96"/>
@@ -14604,16 +14691,16 @@
       <c r="Z23" s="28"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="135"/>
+      <c r="A24" s="154"/>
       <c r="B24" s="97"/>
-      <c r="C24" s="136"/>
+      <c r="C24" s="155"/>
       <c r="D24" s="97"/>
-      <c r="E24" s="136"/>
+      <c r="E24" s="155"/>
       <c r="F24" s="97"/>
-      <c r="G24" s="150"/>
+      <c r="G24" s="136"/>
       <c r="H24" s="96"/>
       <c r="I24" s="97"/>
-      <c r="J24" s="150"/>
+      <c r="J24" s="136"/>
       <c r="K24" s="97"/>
       <c r="L24" s="140"/>
       <c r="M24" s="96"/>
@@ -14632,16 +14719,16 @@
       <c r="Z24" s="28"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="135"/>
+      <c r="A25" s="154"/>
       <c r="B25" s="97"/>
-      <c r="C25" s="136"/>
+      <c r="C25" s="155"/>
       <c r="D25" s="97"/>
-      <c r="E25" s="136"/>
+      <c r="E25" s="155"/>
       <c r="F25" s="97"/>
-      <c r="G25" s="150"/>
+      <c r="G25" s="136"/>
       <c r="H25" s="96"/>
       <c r="I25" s="97"/>
-      <c r="J25" s="150"/>
+      <c r="J25" s="136"/>
       <c r="K25" s="97"/>
       <c r="L25" s="140"/>
       <c r="M25" s="96"/>
@@ -14660,16 +14747,16 @@
       <c r="Z25" s="28"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="135"/>
+      <c r="A26" s="154"/>
       <c r="B26" s="97"/>
-      <c r="C26" s="136"/>
+      <c r="C26" s="155"/>
       <c r="D26" s="97"/>
-      <c r="E26" s="136"/>
+      <c r="E26" s="155"/>
       <c r="F26" s="97"/>
-      <c r="G26" s="150"/>
+      <c r="G26" s="136"/>
       <c r="H26" s="96"/>
       <c r="I26" s="97"/>
-      <c r="J26" s="150"/>
+      <c r="J26" s="136"/>
       <c r="K26" s="97"/>
       <c r="L26" s="140"/>
       <c r="M26" s="96"/>
@@ -14688,16 +14775,16 @@
       <c r="Z26" s="28"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="135"/>
+      <c r="A27" s="154"/>
       <c r="B27" s="97"/>
-      <c r="C27" s="136"/>
+      <c r="C27" s="155"/>
       <c r="D27" s="97"/>
-      <c r="E27" s="136"/>
+      <c r="E27" s="155"/>
       <c r="F27" s="97"/>
-      <c r="G27" s="150"/>
+      <c r="G27" s="136"/>
       <c r="H27" s="96"/>
       <c r="I27" s="97"/>
-      <c r="J27" s="150"/>
+      <c r="J27" s="136"/>
       <c r="K27" s="97"/>
       <c r="L27" s="140"/>
       <c r="M27" s="96"/>
@@ -14716,16 +14803,16 @@
       <c r="Z27" s="28"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="135"/>
+      <c r="A28" s="154"/>
       <c r="B28" s="97"/>
-      <c r="C28" s="136"/>
+      <c r="C28" s="155"/>
       <c r="D28" s="97"/>
-      <c r="E28" s="136"/>
+      <c r="E28" s="155"/>
       <c r="F28" s="97"/>
-      <c r="G28" s="150"/>
+      <c r="G28" s="136"/>
       <c r="H28" s="96"/>
       <c r="I28" s="97"/>
-      <c r="J28" s="150"/>
+      <c r="J28" s="136"/>
       <c r="K28" s="97"/>
       <c r="L28" s="140"/>
       <c r="M28" s="96"/>
@@ -14744,16 +14831,16 @@
       <c r="Z28" s="28"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="135"/>
+      <c r="A29" s="154"/>
       <c r="B29" s="97"/>
-      <c r="C29" s="136"/>
+      <c r="C29" s="155"/>
       <c r="D29" s="97"/>
-      <c r="E29" s="136"/>
+      <c r="E29" s="155"/>
       <c r="F29" s="97"/>
-      <c r="G29" s="150"/>
+      <c r="G29" s="136"/>
       <c r="H29" s="96"/>
       <c r="I29" s="97"/>
-      <c r="J29" s="150"/>
+      <c r="J29" s="136"/>
       <c r="K29" s="97"/>
       <c r="L29" s="140"/>
       <c r="M29" s="96"/>
@@ -14772,16 +14859,16 @@
       <c r="Z29" s="28"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="135"/>
+      <c r="A30" s="154"/>
       <c r="B30" s="97"/>
-      <c r="C30" s="136"/>
+      <c r="C30" s="155"/>
       <c r="D30" s="97"/>
-      <c r="E30" s="136"/>
+      <c r="E30" s="155"/>
       <c r="F30" s="97"/>
-      <c r="G30" s="150"/>
+      <c r="G30" s="136"/>
       <c r="H30" s="96"/>
       <c r="I30" s="97"/>
-      <c r="J30" s="150"/>
+      <c r="J30" s="136"/>
       <c r="K30" s="97"/>
       <c r="L30" s="140"/>
       <c r="M30" s="96"/>
@@ -14800,23 +14887,23 @@
       <c r="Z30" s="28"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="137"/>
-      <c r="B31" s="138"/>
-      <c r="C31" s="139"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="158"/>
-      <c r="H31" s="142"/>
-      <c r="I31" s="138"/>
-      <c r="J31" s="158"/>
-      <c r="K31" s="138"/>
+      <c r="A31" s="157"/>
+      <c r="B31" s="139"/>
+      <c r="C31" s="158"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="137"/>
+      <c r="H31" s="138"/>
+      <c r="I31" s="139"/>
+      <c r="J31" s="137"/>
+      <c r="K31" s="139"/>
       <c r="L31" s="141"/>
-      <c r="M31" s="142"/>
-      <c r="N31" s="138"/>
+      <c r="M31" s="138"/>
+      <c r="N31" s="139"/>
       <c r="O31" s="141"/>
-      <c r="P31" s="142"/>
-      <c r="Q31" s="138"/>
+      <c r="P31" s="138"/>
+      <c r="Q31" s="139"/>
       <c r="R31" s="29"/>
       <c r="S31" s="29"/>
       <c r="T31" s="30"/>
@@ -15814,62 +15901,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -15894,62 +15981,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
